--- a/data/DNAm mice info -BW dataset.xlsx
+++ b/data/DNAm mice info -BW dataset.xlsx
@@ -1,1315 +1,1322 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://emailsc-my.sharepoint.com/personal/huynhdam_email_sc_edu/Documents/Documents/GitHub/Relatedness_pero_DNAm/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_B89231273C89E3C550F739B813FC10FA9A9AAB30" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="430">
-  <si>
-    <t xml:space="preserve">X</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample_Well</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample_Plate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sample_Group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pool_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentrix_ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sentrix_Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExternalSampleName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SampleType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tissue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Species</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Genotype</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TreatmentGroup</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Relatedness</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Well_Address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plate_Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IDATsFound</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExtBasename</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CollectionDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VolCode_HLTH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basename</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Row</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Col</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Project</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Clock_40K_DNA_0019_Plate2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DNA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BW</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET0625.USCKiarisBWrelatedness.m40k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET06259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062510</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220053/208984220053_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062520</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220056/208984220056_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062530</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220060/208984220060_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062540</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220068/208984220068_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062550</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062556</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062560</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220069/208984220069_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062570</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220086/208984220086_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062580</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220095/208984220095_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R01C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R02C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R03C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R04C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R05C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062590</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R06C01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R01C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R02C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R03C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R04C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R05C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ET062596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096_R06C02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">208984220096/208984220096_R06C02</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1179" uniqueCount="430">
+  <si>
+    <t>X</t>
+  </si>
+  <si>
+    <t>SID</t>
+  </si>
+  <si>
+    <t>Sample_Well</t>
+  </si>
+  <si>
+    <t>Sample_Plate</t>
+  </si>
+  <si>
+    <t>Sample_Group</t>
+  </si>
+  <si>
+    <t>Pool_ID</t>
+  </si>
+  <si>
+    <t>Sentrix_ID</t>
+  </si>
+  <si>
+    <t>Sentrix_Position</t>
+  </si>
+  <si>
+    <t>ExternalSampleName</t>
+  </si>
+  <si>
+    <t>SampleType</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Tissue</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Genotype</t>
+  </si>
+  <si>
+    <t>TreatmentGroup</t>
+  </si>
+  <si>
+    <t>Relatedness</t>
+  </si>
+  <si>
+    <t>Well_Address</t>
+  </si>
+  <si>
+    <t>Plate_Number</t>
+  </si>
+  <si>
+    <t>IDATsFound</t>
+  </si>
+  <si>
+    <t>ExtBasename</t>
+  </si>
+  <si>
+    <t>CollectionDate</t>
+  </si>
+  <si>
+    <t>VolCode_HLTH</t>
+  </si>
+  <si>
+    <t>Basename</t>
+  </si>
+  <si>
+    <t>Row</t>
+  </si>
+  <si>
+    <t>Col</t>
+  </si>
+  <si>
+    <t>Project</t>
+  </si>
+  <si>
+    <t>ET06251</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>Clock_40K_DNA_0019_Plate2</t>
+  </si>
+  <si>
+    <t>R01C01</t>
+  </si>
+  <si>
+    <t>DNA</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Tail</t>
+  </si>
+  <si>
+    <t>BW</t>
+  </si>
+  <si>
+    <t>208984220053_R01C01</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R01C01</t>
+  </si>
+  <si>
+    <t>ET0625.USCKiarisBWrelatedness.m40k</t>
+  </si>
+  <si>
+    <t>ET06252</t>
+  </si>
+  <si>
+    <t>B01</t>
+  </si>
+  <si>
+    <t>R02C01</t>
+  </si>
+  <si>
+    <t>208984220053_R02C01</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R02C01</t>
+  </si>
+  <si>
+    <t>ET06253</t>
+  </si>
+  <si>
+    <t>C01</t>
+  </si>
+  <si>
+    <t>R03C01</t>
+  </si>
+  <si>
+    <t>208984220053_R03C01</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R03C01</t>
+  </si>
+  <si>
+    <t>ET06254</t>
+  </si>
+  <si>
+    <t>D01</t>
+  </si>
+  <si>
+    <t>R04C01</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>208984220053_R04C01</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R04C01</t>
+  </si>
+  <si>
+    <t>ET06255</t>
+  </si>
+  <si>
+    <t>E01</t>
+  </si>
+  <si>
+    <t>R05C01</t>
+  </si>
+  <si>
+    <t>208984220053_R05C01</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R05C01</t>
+  </si>
+  <si>
+    <t>ET06256</t>
+  </si>
+  <si>
+    <t>F01</t>
+  </si>
+  <si>
+    <t>R06C01</t>
+  </si>
+  <si>
+    <t>208984220053_R06C01</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R06C01</t>
+  </si>
+  <si>
+    <t>ET06257</t>
+  </si>
+  <si>
+    <t>G01</t>
+  </si>
+  <si>
+    <t>R01C02</t>
+  </si>
+  <si>
+    <t>208984220053_R01C02</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R01C02</t>
+  </si>
+  <si>
+    <t>ET06258</t>
+  </si>
+  <si>
+    <t>H01</t>
+  </si>
+  <si>
+    <t>R02C02</t>
+  </si>
+  <si>
+    <t>208984220053_R02C02</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R02C02</t>
+  </si>
+  <si>
+    <t>ET06259</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>R03C02</t>
+  </si>
+  <si>
+    <t>208984220053_R03C02</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R03C02</t>
+  </si>
+  <si>
+    <t>ET062510</t>
+  </si>
+  <si>
+    <t>B02</t>
+  </si>
+  <si>
+    <t>R04C02</t>
+  </si>
+  <si>
+    <t>208984220053_R04C02</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R04C02</t>
+  </si>
+  <si>
+    <t>ET062511</t>
+  </si>
+  <si>
+    <t>C02</t>
+  </si>
+  <si>
+    <t>R05C02</t>
+  </si>
+  <si>
+    <t>208984220053_R05C02</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R05C02</t>
+  </si>
+  <si>
+    <t>ET062512</t>
+  </si>
+  <si>
+    <t>D02</t>
+  </si>
+  <si>
+    <t>R06C02</t>
+  </si>
+  <si>
+    <t>208984220053_R06C02</t>
+  </si>
+  <si>
+    <t>208984220053/208984220053_R06C02</t>
+  </si>
+  <si>
+    <t>ET062513</t>
+  </si>
+  <si>
+    <t>E02</t>
+  </si>
+  <si>
+    <t>208984220056_R01C01</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R01C01</t>
+  </si>
+  <si>
+    <t>ET062514</t>
+  </si>
+  <si>
+    <t>F02</t>
+  </si>
+  <si>
+    <t>208984220056_R02C01</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R02C01</t>
+  </si>
+  <si>
+    <t>ET062515</t>
+  </si>
+  <si>
+    <t>G02</t>
+  </si>
+  <si>
+    <t>208984220056_R03C01</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R03C01</t>
+  </si>
+  <si>
+    <t>ET062516</t>
+  </si>
+  <si>
+    <t>H02</t>
+  </si>
+  <si>
+    <t>208984220056_R04C01</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R04C01</t>
+  </si>
+  <si>
+    <t>ET062517</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>208984220056_R05C01</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R05C01</t>
+  </si>
+  <si>
+    <t>ET062518</t>
+  </si>
+  <si>
+    <t>B03</t>
+  </si>
+  <si>
+    <t>208984220056_R06C01</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R06C01</t>
+  </si>
+  <si>
+    <t>ET062519</t>
+  </si>
+  <si>
+    <t>C03</t>
+  </si>
+  <si>
+    <t>208984220056_R01C02</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R01C02</t>
+  </si>
+  <si>
+    <t>ET062520</t>
+  </si>
+  <si>
+    <t>D03</t>
+  </si>
+  <si>
+    <t>208984220056_R02C02</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R02C02</t>
+  </si>
+  <si>
+    <t>ET062521</t>
+  </si>
+  <si>
+    <t>E03</t>
+  </si>
+  <si>
+    <t>208984220056_R03C02</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R03C02</t>
+  </si>
+  <si>
+    <t>ET062522</t>
+  </si>
+  <si>
+    <t>F03</t>
+  </si>
+  <si>
+    <t>208984220056_R04C02</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R04C02</t>
+  </si>
+  <si>
+    <t>ET062523</t>
+  </si>
+  <si>
+    <t>G03</t>
+  </si>
+  <si>
+    <t>208984220056_R05C02</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R05C02</t>
+  </si>
+  <si>
+    <t>ET062524</t>
+  </si>
+  <si>
+    <t>H03</t>
+  </si>
+  <si>
+    <t>208984220056_R06C02</t>
+  </si>
+  <si>
+    <t>208984220056/208984220056_R06C02</t>
+  </si>
+  <si>
+    <t>ET062525</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>208984220060_R01C01</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R01C01</t>
+  </si>
+  <si>
+    <t>ET062526</t>
+  </si>
+  <si>
+    <t>B04</t>
+  </si>
+  <si>
+    <t>208984220060_R02C01</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R02C01</t>
+  </si>
+  <si>
+    <t>ET062527</t>
+  </si>
+  <si>
+    <t>C04</t>
+  </si>
+  <si>
+    <t>208984220060_R03C01</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R03C01</t>
+  </si>
+  <si>
+    <t>ET062528</t>
+  </si>
+  <si>
+    <t>D04</t>
+  </si>
+  <si>
+    <t>208984220060_R04C01</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R04C01</t>
+  </si>
+  <si>
+    <t>ET062529</t>
+  </si>
+  <si>
+    <t>E04</t>
+  </si>
+  <si>
+    <t>208984220060_R05C01</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R05C01</t>
+  </si>
+  <si>
+    <t>ET062530</t>
+  </si>
+  <si>
+    <t>F04</t>
+  </si>
+  <si>
+    <t>208984220060_R06C01</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R06C01</t>
+  </si>
+  <si>
+    <t>ET062531</t>
+  </si>
+  <si>
+    <t>G04</t>
+  </si>
+  <si>
+    <t>208984220060_R01C02</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R01C02</t>
+  </si>
+  <si>
+    <t>ET062532</t>
+  </si>
+  <si>
+    <t>H04</t>
+  </si>
+  <si>
+    <t>208984220060_R02C02</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R02C02</t>
+  </si>
+  <si>
+    <t>ET062533</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>208984220060_R03C02</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R03C02</t>
+  </si>
+  <si>
+    <t>ET062534</t>
+  </si>
+  <si>
+    <t>B05</t>
+  </si>
+  <si>
+    <t>208984220060_R04C02</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R04C02</t>
+  </si>
+  <si>
+    <t>ET062535</t>
+  </si>
+  <si>
+    <t>C05</t>
+  </si>
+  <si>
+    <t>208984220060_R05C02</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R05C02</t>
+  </si>
+  <si>
+    <t>ET062536</t>
+  </si>
+  <si>
+    <t>D05</t>
+  </si>
+  <si>
+    <t>208984220060_R06C02</t>
+  </si>
+  <si>
+    <t>208984220060/208984220060_R06C02</t>
+  </si>
+  <si>
+    <t>ET062537</t>
+  </si>
+  <si>
+    <t>E05</t>
+  </si>
+  <si>
+    <t>208984220068_R01C01</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R01C01</t>
+  </si>
+  <si>
+    <t>ET062538</t>
+  </si>
+  <si>
+    <t>F05</t>
+  </si>
+  <si>
+    <t>208984220068_R02C01</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R02C01</t>
+  </si>
+  <si>
+    <t>ET062539</t>
+  </si>
+  <si>
+    <t>G05</t>
+  </si>
+  <si>
+    <t>208984220068_R03C01</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R03C01</t>
+  </si>
+  <si>
+    <t>ET062540</t>
+  </si>
+  <si>
+    <t>H05</t>
+  </si>
+  <si>
+    <t>208984220068_R04C01</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R04C01</t>
+  </si>
+  <si>
+    <t>ET062541</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>208984220068_R05C01</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R05C01</t>
+  </si>
+  <si>
+    <t>ET062542</t>
+  </si>
+  <si>
+    <t>B06</t>
+  </si>
+  <si>
+    <t>208984220068_R06C01</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R06C01</t>
+  </si>
+  <si>
+    <t>ET062543</t>
+  </si>
+  <si>
+    <t>C06</t>
+  </si>
+  <si>
+    <t>208984220068_R01C02</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R01C02</t>
+  </si>
+  <si>
+    <t>ET062544</t>
+  </si>
+  <si>
+    <t>D06</t>
+  </si>
+  <si>
+    <t>208984220068_R02C02</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R02C02</t>
+  </si>
+  <si>
+    <t>ET062545</t>
+  </si>
+  <si>
+    <t>E06</t>
+  </si>
+  <si>
+    <t>208984220068_R03C02</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R03C02</t>
+  </si>
+  <si>
+    <t>ET062546</t>
+  </si>
+  <si>
+    <t>F06</t>
+  </si>
+  <si>
+    <t>208984220068_R04C02</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R04C02</t>
+  </si>
+  <si>
+    <t>ET062547</t>
+  </si>
+  <si>
+    <t>G06</t>
+  </si>
+  <si>
+    <t>208984220068_R05C02</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R05C02</t>
+  </si>
+  <si>
+    <t>ET062548</t>
+  </si>
+  <si>
+    <t>H06</t>
+  </si>
+  <si>
+    <t>208984220068_R06C02</t>
+  </si>
+  <si>
+    <t>208984220068/208984220068_R06C02</t>
+  </si>
+  <si>
+    <t>ET062549</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>208984220069_R01C01</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R01C01</t>
+  </si>
+  <si>
+    <t>ET062550</t>
+  </si>
+  <si>
+    <t>B07</t>
+  </si>
+  <si>
+    <t>208984220069_R02C01</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R02C01</t>
+  </si>
+  <si>
+    <t>ET062551</t>
+  </si>
+  <si>
+    <t>C07</t>
+  </si>
+  <si>
+    <t>208984220069_R03C01</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R03C01</t>
+  </si>
+  <si>
+    <t>ET062552</t>
+  </si>
+  <si>
+    <t>D07</t>
+  </si>
+  <si>
+    <t>208984220069_R04C01</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R04C01</t>
+  </si>
+  <si>
+    <t>ET062553</t>
+  </si>
+  <si>
+    <t>E07</t>
+  </si>
+  <si>
+    <t>208984220069_R05C01</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R05C01</t>
+  </si>
+  <si>
+    <t>ET062554</t>
+  </si>
+  <si>
+    <t>F07</t>
+  </si>
+  <si>
+    <t>208984220069_R06C01</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R06C01</t>
+  </si>
+  <si>
+    <t>ET062555</t>
+  </si>
+  <si>
+    <t>G07</t>
+  </si>
+  <si>
+    <t>208984220069_R01C02</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R01C02</t>
+  </si>
+  <si>
+    <t>ET062556</t>
+  </si>
+  <si>
+    <t>H07</t>
+  </si>
+  <si>
+    <t>208984220069_R02C02</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R02C02</t>
+  </si>
+  <si>
+    <t>ET062557</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>208984220069_R03C02</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R03C02</t>
+  </si>
+  <si>
+    <t>ET062558</t>
+  </si>
+  <si>
+    <t>B08</t>
+  </si>
+  <si>
+    <t>208984220069_R04C02</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R04C02</t>
+  </si>
+  <si>
+    <t>ET062559</t>
+  </si>
+  <si>
+    <t>C08</t>
+  </si>
+  <si>
+    <t>208984220069_R05C02</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R05C02</t>
+  </si>
+  <si>
+    <t>ET062560</t>
+  </si>
+  <si>
+    <t>D08</t>
+  </si>
+  <si>
+    <t>208984220069_R06C02</t>
+  </si>
+  <si>
+    <t>208984220069/208984220069_R06C02</t>
+  </si>
+  <si>
+    <t>ET062561</t>
+  </si>
+  <si>
+    <t>E08</t>
+  </si>
+  <si>
+    <t>208984220086_R01C01</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R01C01</t>
+  </si>
+  <si>
+    <t>ET062562</t>
+  </si>
+  <si>
+    <t>F08</t>
+  </si>
+  <si>
+    <t>208984220086_R02C01</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R02C01</t>
+  </si>
+  <si>
+    <t>ET062563</t>
+  </si>
+  <si>
+    <t>G08</t>
+  </si>
+  <si>
+    <t>208984220086_R03C01</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R03C01</t>
+  </si>
+  <si>
+    <t>ET062564</t>
+  </si>
+  <si>
+    <t>H08</t>
+  </si>
+  <si>
+    <t>208984220086_R04C01</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R04C01</t>
+  </si>
+  <si>
+    <t>ET062565</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>208984220086_R05C01</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R05C01</t>
+  </si>
+  <si>
+    <t>ET062566</t>
+  </si>
+  <si>
+    <t>B09</t>
+  </si>
+  <si>
+    <t>208984220086_R06C01</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R06C01</t>
+  </si>
+  <si>
+    <t>ET062567</t>
+  </si>
+  <si>
+    <t>C09</t>
+  </si>
+  <si>
+    <t>208984220086_R01C02</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R01C02</t>
+  </si>
+  <si>
+    <t>ET062568</t>
+  </si>
+  <si>
+    <t>D09</t>
+  </si>
+  <si>
+    <t>208984220086_R02C02</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R02C02</t>
+  </si>
+  <si>
+    <t>ET062569</t>
+  </si>
+  <si>
+    <t>E09</t>
+  </si>
+  <si>
+    <t>208984220086_R03C02</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R03C02</t>
+  </si>
+  <si>
+    <t>ET062570</t>
+  </si>
+  <si>
+    <t>F09</t>
+  </si>
+  <si>
+    <t>208984220086_R04C02</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R04C02</t>
+  </si>
+  <si>
+    <t>ET062571</t>
+  </si>
+  <si>
+    <t>G09</t>
+  </si>
+  <si>
+    <t>208984220086_R05C02</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R05C02</t>
+  </si>
+  <si>
+    <t>ET062572</t>
+  </si>
+  <si>
+    <t>H09</t>
+  </si>
+  <si>
+    <t>208984220086_R06C02</t>
+  </si>
+  <si>
+    <t>208984220086/208984220086_R06C02</t>
+  </si>
+  <si>
+    <t>ET062573</t>
+  </si>
+  <si>
+    <t>A10</t>
+  </si>
+  <si>
+    <t>208984220095_R01C01</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R01C01</t>
+  </si>
+  <si>
+    <t>ET062574</t>
+  </si>
+  <si>
+    <t>B10</t>
+  </si>
+  <si>
+    <t>208984220095_R02C01</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R02C01</t>
+  </si>
+  <si>
+    <t>ET062575</t>
+  </si>
+  <si>
+    <t>C10</t>
+  </si>
+  <si>
+    <t>208984220095_R03C01</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R03C01</t>
+  </si>
+  <si>
+    <t>ET062576</t>
+  </si>
+  <si>
+    <t>D10</t>
+  </si>
+  <si>
+    <t>208984220095_R04C01</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R04C01</t>
+  </si>
+  <si>
+    <t>ET062577</t>
+  </si>
+  <si>
+    <t>E10</t>
+  </si>
+  <si>
+    <t>208984220095_R05C01</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R05C01</t>
+  </si>
+  <si>
+    <t>ET062578</t>
+  </si>
+  <si>
+    <t>F10</t>
+  </si>
+  <si>
+    <t>208984220095_R06C01</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R06C01</t>
+  </si>
+  <si>
+    <t>ET062579</t>
+  </si>
+  <si>
+    <t>G10</t>
+  </si>
+  <si>
+    <t>208984220095_R01C02</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R01C02</t>
+  </si>
+  <si>
+    <t>ET062580</t>
+  </si>
+  <si>
+    <t>H10</t>
+  </si>
+  <si>
+    <t>208984220095_R02C02</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R02C02</t>
+  </si>
+  <si>
+    <t>ET062581</t>
+  </si>
+  <si>
+    <t>A11</t>
+  </si>
+  <si>
+    <t>208984220095_R03C02</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R03C02</t>
+  </si>
+  <si>
+    <t>ET062582</t>
+  </si>
+  <si>
+    <t>B11</t>
+  </si>
+  <si>
+    <t>208984220095_R04C02</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R04C02</t>
+  </si>
+  <si>
+    <t>ET062583</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>208984220095_R05C02</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R05C02</t>
+  </si>
+  <si>
+    <t>ET062584</t>
+  </si>
+  <si>
+    <t>D11</t>
+  </si>
+  <si>
+    <t>208984220095_R06C02</t>
+  </si>
+  <si>
+    <t>208984220095/208984220095_R06C02</t>
+  </si>
+  <si>
+    <t>ET062585</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>208984220096_R01C01</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R01C01</t>
+  </si>
+  <si>
+    <t>ET062586</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>208984220096_R02C01</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R02C01</t>
+  </si>
+  <si>
+    <t>ET062587</t>
+  </si>
+  <si>
+    <t>G11</t>
+  </si>
+  <si>
+    <t>208984220096_R03C01</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R03C01</t>
+  </si>
+  <si>
+    <t>ET062588</t>
+  </si>
+  <si>
+    <t>H11</t>
+  </si>
+  <si>
+    <t>208984220096_R04C01</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R04C01</t>
+  </si>
+  <si>
+    <t>ET062589</t>
+  </si>
+  <si>
+    <t>A12</t>
+  </si>
+  <si>
+    <t>208984220096_R05C01</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R05C01</t>
+  </si>
+  <si>
+    <t>ET062590</t>
+  </si>
+  <si>
+    <t>B12</t>
+  </si>
+  <si>
+    <t>208984220096_R06C01</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R06C01</t>
+  </si>
+  <si>
+    <t>ET062591</t>
+  </si>
+  <si>
+    <t>C12</t>
+  </si>
+  <si>
+    <t>208984220096_R01C02</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R01C02</t>
+  </si>
+  <si>
+    <t>ET062592</t>
+  </si>
+  <si>
+    <t>D12</t>
+  </si>
+  <si>
+    <t>208984220096_R02C02</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R02C02</t>
+  </si>
+  <si>
+    <t>ET062593</t>
+  </si>
+  <si>
+    <t>E12</t>
+  </si>
+  <si>
+    <t>208984220096_R03C02</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R03C02</t>
+  </si>
+  <si>
+    <t>ET062594</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>208984220096_R04C02</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R04C02</t>
+  </si>
+  <si>
+    <t>ET062595</t>
+  </si>
+  <si>
+    <t>G12</t>
+  </si>
+  <si>
+    <t>208984220096_R05C02</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R05C02</t>
+  </si>
+  <si>
+    <t>ET062596</t>
+  </si>
+  <si>
+    <t>H12</t>
+  </si>
+  <si>
+    <t>208984220096_R06C02</t>
+  </si>
+  <si>
+    <t>208984220096/208984220096_R06C02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1345,6 +1352,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1626,11 +1642,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AA97"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1713,8 +1729,8 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -1729,21 +1745,20 @@
       <c r="E2" t="s">
         <v>27</v>
       </c>
-      <c r="F2"/>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>208984000000</v>
       </c>
       <c r="H2" t="s">
         <v>30</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>40136</v>
       </c>
       <c r="J2" t="s">
         <v>31</v>
       </c>
-      <c r="K2" t="n">
-        <v>0.233</v>
+      <c r="K2">
+        <v>0.23300000000000001</v>
       </c>
       <c r="L2" t="s">
         <v>32</v>
@@ -1754,36 +1769,30 @@
       <c r="N2" t="s">
         <v>34</v>
       </c>
-      <c r="O2"/>
-      <c r="P2"/>
-      <c r="Q2" t="n">
+      <c r="Q2">
         <v>21.5</v>
       </c>
-      <c r="R2"/>
-      <c r="S2"/>
       <c r="T2" t="b">
         <v>0</v>
       </c>
       <c r="U2" t="s">
         <v>35</v>
       </c>
-      <c r="V2"/>
-      <c r="W2"/>
       <c r="X2" t="s">
         <v>36</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="Y2">
         <v>1</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="Z2">
         <v>1</v>
       </c>
       <c r="AA2" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
@@ -1798,21 +1807,20 @@
       <c r="E3" t="s">
         <v>38</v>
       </c>
-      <c r="F3"/>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>208984000000</v>
       </c>
       <c r="H3" t="s">
         <v>40</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>39898</v>
       </c>
       <c r="J3" t="s">
         <v>31</v>
       </c>
-      <c r="K3" t="n">
-        <v>1.481</v>
+      <c r="K3">
+        <v>1.4810000000000001</v>
       </c>
       <c r="L3" t="s">
         <v>32</v>
@@ -1823,36 +1831,30 @@
       <c r="N3" t="s">
         <v>34</v>
       </c>
-      <c r="O3"/>
-      <c r="P3"/>
-      <c r="Q3" t="n">
+      <c r="Q3">
         <v>14.4</v>
       </c>
-      <c r="R3"/>
-      <c r="S3"/>
       <c r="T3" t="b">
         <v>0</v>
       </c>
       <c r="U3" t="s">
         <v>41</v>
       </c>
-      <c r="V3"/>
-      <c r="W3"/>
       <c r="X3" t="s">
         <v>42</v>
       </c>
-      <c r="Y3" t="n">
+      <c r="Y3">
         <v>2</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="Z3">
         <v>1</v>
       </c>
       <c r="AA3" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -1867,20 +1869,19 @@
       <c r="E4" t="s">
         <v>43</v>
       </c>
-      <c r="F4"/>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>208984000000</v>
       </c>
       <c r="H4" t="s">
         <v>45</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>38962</v>
       </c>
       <c r="J4" t="s">
         <v>31</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>2.76</v>
       </c>
       <c r="L4" t="s">
@@ -1892,36 +1893,30 @@
       <c r="N4" t="s">
         <v>34</v>
       </c>
-      <c r="O4"/>
-      <c r="P4"/>
-      <c r="Q4" t="n">
+      <c r="Q4">
         <v>86.9</v>
       </c>
-      <c r="R4"/>
-      <c r="S4"/>
       <c r="T4" t="b">
         <v>0</v>
       </c>
       <c r="U4" t="s">
         <v>46</v>
       </c>
-      <c r="V4"/>
-      <c r="W4"/>
       <c r="X4" t="s">
         <v>47</v>
       </c>
-      <c r="Y4" t="n">
+      <c r="Y4">
         <v>3</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="Z4">
         <v>1</v>
       </c>
       <c r="AA4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
@@ -1936,20 +1931,19 @@
       <c r="E5" t="s">
         <v>48</v>
       </c>
-      <c r="F5"/>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>208984000000</v>
       </c>
       <c r="H5" t="s">
         <v>50</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>39651</v>
       </c>
       <c r="J5" t="s">
         <v>31</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>1.81</v>
       </c>
       <c r="L5" t="s">
@@ -1961,36 +1955,30 @@
       <c r="N5" t="s">
         <v>34</v>
       </c>
-      <c r="O5"/>
-      <c r="P5"/>
-      <c r="Q5" t="n">
+      <c r="Q5">
         <v>31.1</v>
       </c>
-      <c r="R5"/>
-      <c r="S5"/>
       <c r="T5" t="b">
         <v>0</v>
       </c>
       <c r="U5" t="s">
         <v>52</v>
       </c>
-      <c r="V5"/>
-      <c r="W5"/>
       <c r="X5" t="s">
         <v>53</v>
       </c>
-      <c r="Y5" t="n">
+      <c r="Y5">
         <v>4</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="Z5">
         <v>1</v>
       </c>
       <c r="AA5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
@@ -2005,20 +1993,19 @@
       <c r="E6" t="s">
         <v>54</v>
       </c>
-      <c r="F6"/>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>208984000000</v>
       </c>
       <c r="H6" t="s">
         <v>56</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>39722</v>
       </c>
       <c r="J6" t="s">
         <v>31</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>1.744</v>
       </c>
       <c r="L6" t="s">
@@ -2030,36 +2017,30 @@
       <c r="N6" t="s">
         <v>34</v>
       </c>
-      <c r="O6"/>
-      <c r="P6"/>
-      <c r="Q6" t="n">
+      <c r="Q6">
         <v>13.9</v>
       </c>
-      <c r="R6"/>
-      <c r="S6"/>
       <c r="T6" t="b">
         <v>0</v>
       </c>
       <c r="U6" t="s">
         <v>57</v>
       </c>
-      <c r="V6"/>
-      <c r="W6"/>
       <c r="X6" t="s">
         <v>58</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="Y6">
         <v>5</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="Z6">
         <v>1</v>
       </c>
       <c r="AA6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
@@ -2074,21 +2055,20 @@
       <c r="E7" t="s">
         <v>59</v>
       </c>
-      <c r="F7"/>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>208984000000</v>
       </c>
       <c r="H7" t="s">
         <v>61</v>
       </c>
-      <c r="I7" t="n">
+      <c r="I7">
         <v>40129</v>
       </c>
       <c r="J7" t="s">
         <v>31</v>
       </c>
-      <c r="K7" t="n">
-        <v>0.285</v>
+      <c r="K7">
+        <v>0.28499999999999998</v>
       </c>
       <c r="L7" t="s">
         <v>51</v>
@@ -2099,36 +2079,30 @@
       <c r="N7" t="s">
         <v>34</v>
       </c>
-      <c r="O7"/>
-      <c r="P7"/>
-      <c r="Q7" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R7"/>
-      <c r="S7"/>
+      <c r="Q7">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T7" t="b">
         <v>0</v>
       </c>
       <c r="U7" t="s">
         <v>62</v>
       </c>
-      <c r="V7"/>
-      <c r="W7"/>
       <c r="X7" t="s">
         <v>63</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="Y7">
         <v>6</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="Z7">
         <v>1</v>
       </c>
       <c r="AA7" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="n">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
@@ -2143,20 +2117,19 @@
       <c r="E8" t="s">
         <v>64</v>
       </c>
-      <c r="F8"/>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>208984000000</v>
       </c>
       <c r="H8" t="s">
         <v>66</v>
       </c>
-      <c r="I8" t="n">
+      <c r="I8">
         <v>39686</v>
       </c>
       <c r="J8" t="s">
         <v>31</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K8">
         <v>1.829</v>
       </c>
       <c r="L8" t="s">
@@ -2168,36 +2141,30 @@
       <c r="N8" t="s">
         <v>34</v>
       </c>
-      <c r="O8"/>
-      <c r="P8"/>
-      <c r="Q8" t="n">
+      <c r="Q8">
         <v>13.9</v>
       </c>
-      <c r="R8"/>
-      <c r="S8"/>
       <c r="T8" t="b">
         <v>0</v>
       </c>
       <c r="U8" t="s">
         <v>67</v>
       </c>
-      <c r="V8"/>
-      <c r="W8"/>
       <c r="X8" t="s">
         <v>68</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="Y8">
         <v>1</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="Z8">
         <v>2</v>
       </c>
       <c r="AA8" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="n">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
@@ -2212,21 +2179,20 @@
       <c r="E9" t="s">
         <v>69</v>
       </c>
-      <c r="F9"/>
-      <c r="G9" t="n">
+      <c r="G9">
         <v>208984000000</v>
       </c>
       <c r="H9" t="s">
         <v>71</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I9">
         <v>40058</v>
       </c>
       <c r="J9" t="s">
         <v>31</v>
       </c>
-      <c r="K9" t="n">
-        <v>0.539</v>
+      <c r="K9">
+        <v>0.53900000000000003</v>
       </c>
       <c r="L9" t="s">
         <v>32</v>
@@ -2237,36 +2203,30 @@
       <c r="N9" t="s">
         <v>34</v>
       </c>
-      <c r="O9"/>
-      <c r="P9"/>
-      <c r="Q9" t="n">
+      <c r="Q9">
         <v>19.3</v>
       </c>
-      <c r="R9"/>
-      <c r="S9"/>
       <c r="T9" t="b">
         <v>0</v>
       </c>
       <c r="U9" t="s">
         <v>72</v>
       </c>
-      <c r="V9"/>
-      <c r="W9"/>
       <c r="X9" t="s">
         <v>73</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="Y9">
         <v>2</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="Z9">
         <v>2</v>
       </c>
       <c r="AA9" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="n">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
@@ -2281,20 +2241,19 @@
       <c r="E10" t="s">
         <v>74</v>
       </c>
-      <c r="F10"/>
-      <c r="G10" t="n">
+      <c r="G10">
         <v>208984000000</v>
       </c>
       <c r="H10" t="s">
         <v>76</v>
       </c>
-      <c r="I10" t="n">
+      <c r="I10">
         <v>40133</v>
       </c>
       <c r="J10" t="s">
         <v>31</v>
       </c>
-      <c r="K10" t="n">
+      <c r="K10">
         <v>0.246</v>
       </c>
       <c r="L10" t="s">
@@ -2306,36 +2265,30 @@
       <c r="N10" t="s">
         <v>34</v>
       </c>
-      <c r="O10"/>
-      <c r="P10"/>
-      <c r="Q10" t="n">
+      <c r="Q10">
         <v>21.5</v>
       </c>
-      <c r="R10"/>
-      <c r="S10"/>
       <c r="T10" t="b">
         <v>0</v>
       </c>
       <c r="U10" t="s">
         <v>77</v>
       </c>
-      <c r="V10"/>
-      <c r="W10"/>
       <c r="X10" t="s">
         <v>78</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y10">
         <v>3</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z10">
         <v>2</v>
       </c>
       <c r="AA10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="n">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
@@ -2350,21 +2303,20 @@
       <c r="E11" t="s">
         <v>79</v>
       </c>
-      <c r="F11"/>
-      <c r="G11" t="n">
+      <c r="G11">
         <v>208984000000</v>
       </c>
       <c r="H11" t="s">
         <v>81</v>
       </c>
-      <c r="I11" t="n">
+      <c r="I11">
         <v>40029</v>
       </c>
       <c r="J11" t="s">
         <v>31</v>
       </c>
-      <c r="K11" t="n">
-        <v>0.931</v>
+      <c r="K11">
+        <v>0.93100000000000005</v>
       </c>
       <c r="L11" t="s">
         <v>51</v>
@@ -2375,36 +2327,30 @@
       <c r="N11" t="s">
         <v>34</v>
       </c>
-      <c r="O11"/>
-      <c r="P11"/>
-      <c r="Q11" t="n">
+      <c r="Q11">
         <v>23.8</v>
       </c>
-      <c r="R11"/>
-      <c r="S11"/>
       <c r="T11" t="b">
         <v>0</v>
       </c>
       <c r="U11" t="s">
         <v>82</v>
       </c>
-      <c r="V11"/>
-      <c r="W11"/>
       <c r="X11" t="s">
         <v>83</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="Y11">
         <v>4</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="Z11">
         <v>2</v>
       </c>
       <c r="AA11" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
@@ -2419,21 +2365,20 @@
       <c r="E12" t="s">
         <v>84</v>
       </c>
-      <c r="F12"/>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>208984000000</v>
       </c>
       <c r="H12" t="s">
         <v>86</v>
       </c>
-      <c r="I12" t="n">
+      <c r="I12">
         <v>39827</v>
       </c>
       <c r="J12" t="s">
         <v>31</v>
       </c>
-      <c r="K12" t="n">
-        <v>1.648186174</v>
+      <c r="K12">
+        <v>1.6481861739999999</v>
       </c>
       <c r="L12" t="s">
         <v>51</v>
@@ -2444,36 +2389,30 @@
       <c r="N12" t="s">
         <v>34</v>
       </c>
-      <c r="O12"/>
-      <c r="P12"/>
-      <c r="Q12" t="n">
+      <c r="Q12">
         <v>31.8</v>
       </c>
-      <c r="R12"/>
-      <c r="S12"/>
       <c r="T12" t="b">
         <v>0</v>
       </c>
       <c r="U12" t="s">
         <v>87</v>
       </c>
-      <c r="V12"/>
-      <c r="W12"/>
       <c r="X12" t="s">
         <v>88</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="Y12">
         <v>5</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="Z12">
         <v>2</v>
       </c>
       <c r="AA12" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="n">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" t="s">
@@ -2488,21 +2427,20 @@
       <c r="E13" t="s">
         <v>89</v>
       </c>
-      <c r="F13"/>
-      <c r="G13" t="n">
+      <c r="G13">
         <v>208984000000</v>
       </c>
       <c r="H13" t="s">
         <v>91</v>
       </c>
-      <c r="I13" t="n">
+      <c r="I13">
         <v>40155</v>
       </c>
       <c r="J13" t="s">
         <v>31</v>
       </c>
-      <c r="K13" t="n">
-        <v>0.203</v>
+      <c r="K13">
+        <v>0.20300000000000001</v>
       </c>
       <c r="L13" t="s">
         <v>32</v>
@@ -2513,36 +2451,30 @@
       <c r="N13" t="s">
         <v>34</v>
       </c>
-      <c r="O13"/>
-      <c r="P13"/>
-      <c r="Q13" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R13"/>
-      <c r="S13"/>
+      <c r="Q13">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T13" t="b">
         <v>0</v>
       </c>
       <c r="U13" t="s">
         <v>92</v>
       </c>
-      <c r="V13"/>
-      <c r="W13"/>
       <c r="X13" t="s">
         <v>93</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="Y13">
         <v>6</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="Z13">
         <v>2</v>
       </c>
       <c r="AA13" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="n">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" t="s">
@@ -2557,21 +2489,20 @@
       <c r="E14" t="s">
         <v>94</v>
       </c>
-      <c r="F14"/>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>208984000000</v>
       </c>
       <c r="H14" t="s">
         <v>30</v>
       </c>
-      <c r="I14" t="n">
+      <c r="I14">
         <v>39389</v>
       </c>
       <c r="J14" t="s">
         <v>31</v>
       </c>
-      <c r="K14" t="n">
-        <v>2.341</v>
+      <c r="K14">
+        <v>2.3410000000000002</v>
       </c>
       <c r="L14" t="s">
         <v>51</v>
@@ -2582,36 +2513,30 @@
       <c r="N14" t="s">
         <v>34</v>
       </c>
-      <c r="O14"/>
-      <c r="P14"/>
-      <c r="Q14" t="n">
+      <c r="Q14">
         <v>14.9</v>
       </c>
-      <c r="R14"/>
-      <c r="S14"/>
       <c r="T14" t="b">
         <v>0</v>
       </c>
       <c r="U14" t="s">
         <v>96</v>
       </c>
-      <c r="V14"/>
-      <c r="W14"/>
       <c r="X14" t="s">
         <v>97</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="Y14">
         <v>1</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="Z14">
         <v>1</v>
       </c>
       <c r="AA14" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" t="n">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" t="s">
@@ -2626,20 +2551,19 @@
       <c r="E15" t="s">
         <v>98</v>
       </c>
-      <c r="F15"/>
-      <c r="G15" t="n">
+      <c r="G15">
         <v>208984000000</v>
       </c>
       <c r="H15" t="s">
         <v>40</v>
       </c>
-      <c r="I15" t="n">
+      <c r="I15">
         <v>39365</v>
       </c>
       <c r="J15" t="s">
         <v>31</v>
       </c>
-      <c r="K15" t="n">
+      <c r="K15">
         <v>2.36</v>
       </c>
       <c r="L15" t="s">
@@ -2651,36 +2575,30 @@
       <c r="N15" t="s">
         <v>34</v>
       </c>
-      <c r="O15"/>
-      <c r="P15"/>
-      <c r="Q15" t="n">
+      <c r="Q15">
         <v>16.2</v>
       </c>
-      <c r="R15"/>
-      <c r="S15"/>
       <c r="T15" t="b">
         <v>0</v>
       </c>
       <c r="U15" t="s">
         <v>100</v>
       </c>
-      <c r="V15"/>
-      <c r="W15"/>
       <c r="X15" t="s">
         <v>101</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="Y15">
         <v>2</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="Z15">
         <v>1</v>
       </c>
       <c r="AA15" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="n">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" t="s">
@@ -2695,21 +2613,20 @@
       <c r="E16" t="s">
         <v>102</v>
       </c>
-      <c r="F16"/>
-      <c r="G16" t="n">
+      <c r="G16">
         <v>208984000000</v>
       </c>
       <c r="H16" t="s">
         <v>45</v>
       </c>
-      <c r="I16" t="n">
+      <c r="I16">
         <v>40032</v>
       </c>
       <c r="J16" t="s">
         <v>31</v>
       </c>
-      <c r="K16" t="n">
-        <v>0.808</v>
+      <c r="K16">
+        <v>0.80800000000000005</v>
       </c>
       <c r="L16" t="s">
         <v>51</v>
@@ -2720,36 +2637,30 @@
       <c r="N16" t="s">
         <v>34</v>
       </c>
-      <c r="O16"/>
-      <c r="P16"/>
-      <c r="Q16" t="n">
+      <c r="Q16">
         <v>15.6</v>
       </c>
-      <c r="R16"/>
-      <c r="S16"/>
       <c r="T16" t="b">
         <v>0</v>
       </c>
       <c r="U16" t="s">
         <v>104</v>
       </c>
-      <c r="V16"/>
-      <c r="W16"/>
       <c r="X16" t="s">
         <v>105</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y16">
         <v>3</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z16">
         <v>1</v>
       </c>
       <c r="AA16" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="n">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" t="s">
@@ -2764,21 +2675,20 @@
       <c r="E17" t="s">
         <v>106</v>
       </c>
-      <c r="F17"/>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>208984000000</v>
       </c>
       <c r="H17" t="s">
         <v>50</v>
       </c>
-      <c r="I17" t="n">
+      <c r="I17">
         <v>40099</v>
       </c>
       <c r="J17" t="s">
         <v>31</v>
       </c>
-      <c r="K17" t="n">
-        <v>0.356</v>
+      <c r="K17">
+        <v>0.35599999999999998</v>
       </c>
       <c r="L17" t="s">
         <v>32</v>
@@ -2789,36 +2699,30 @@
       <c r="N17" t="s">
         <v>34</v>
       </c>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R17"/>
-      <c r="S17"/>
+      <c r="Q17">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T17" t="b">
         <v>0</v>
       </c>
       <c r="U17" t="s">
         <v>108</v>
       </c>
-      <c r="V17"/>
-      <c r="W17"/>
       <c r="X17" t="s">
         <v>109</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="Y17">
         <v>4</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="Z17">
         <v>1</v>
       </c>
       <c r="AA17" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="n">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" t="s">
@@ -2833,20 +2737,19 @@
       <c r="E18" t="s">
         <v>110</v>
       </c>
-      <c r="F18"/>
-      <c r="G18" t="n">
+      <c r="G18">
         <v>208984000000</v>
       </c>
       <c r="H18" t="s">
         <v>56</v>
       </c>
-      <c r="I18" t="n">
+      <c r="I18">
         <v>39360</v>
       </c>
       <c r="J18" t="s">
         <v>31</v>
       </c>
-      <c r="K18" t="n">
+      <c r="K18">
         <v>2.371</v>
       </c>
       <c r="L18" t="s">
@@ -2858,36 +2761,30 @@
       <c r="N18" t="s">
         <v>34</v>
       </c>
-      <c r="O18"/>
-      <c r="P18"/>
-      <c r="Q18" t="n">
+      <c r="Q18">
         <v>41.4</v>
       </c>
-      <c r="R18"/>
-      <c r="S18"/>
       <c r="T18" t="b">
         <v>0</v>
       </c>
       <c r="U18" t="s">
         <v>112</v>
       </c>
-      <c r="V18"/>
-      <c r="W18"/>
       <c r="X18" t="s">
         <v>113</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="Y18">
         <v>5</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="Z18">
         <v>1</v>
       </c>
       <c r="AA18" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="n">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
@@ -2902,21 +2799,20 @@
       <c r="E19" t="s">
         <v>114</v>
       </c>
-      <c r="F19"/>
-      <c r="G19" t="n">
+      <c r="G19">
         <v>208984000000</v>
       </c>
       <c r="H19" t="s">
         <v>61</v>
       </c>
-      <c r="I19" t="n">
+      <c r="I19">
         <v>40071</v>
       </c>
       <c r="J19" t="s">
         <v>31</v>
       </c>
-      <c r="K19" t="n">
-        <v>0.452</v>
+      <c r="K19">
+        <v>0.45200000000000001</v>
       </c>
       <c r="L19" t="s">
         <v>51</v>
@@ -2927,36 +2823,30 @@
       <c r="N19" t="s">
         <v>34</v>
       </c>
-      <c r="O19"/>
-      <c r="P19"/>
-      <c r="Q19" t="n">
+      <c r="Q19">
         <v>26.4</v>
       </c>
-      <c r="R19"/>
-      <c r="S19"/>
       <c r="T19" t="b">
         <v>0</v>
       </c>
       <c r="U19" t="s">
         <v>116</v>
       </c>
-      <c r="V19"/>
-      <c r="W19"/>
       <c r="X19" t="s">
         <v>117</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="Y19">
         <v>6</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="Z19">
         <v>1</v>
       </c>
       <c r="AA19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="n">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
@@ -2971,20 +2861,19 @@
       <c r="E20" t="s">
         <v>118</v>
       </c>
-      <c r="F20"/>
-      <c r="G20" t="n">
+      <c r="G20">
         <v>208984000000</v>
       </c>
       <c r="H20" t="s">
         <v>66</v>
       </c>
-      <c r="I20" t="n">
+      <c r="I20">
         <v>39835</v>
       </c>
       <c r="J20" t="s">
         <v>31</v>
       </c>
-      <c r="K20" t="n">
+      <c r="K20">
         <v>1.591</v>
       </c>
       <c r="L20" t="s">
@@ -2996,36 +2885,30 @@
       <c r="N20" t="s">
         <v>34</v>
       </c>
-      <c r="O20"/>
-      <c r="P20"/>
-      <c r="Q20" t="n">
+      <c r="Q20">
         <v>34.4</v>
       </c>
-      <c r="R20"/>
-      <c r="S20"/>
       <c r="T20" t="b">
         <v>0</v>
       </c>
       <c r="U20" t="s">
         <v>120</v>
       </c>
-      <c r="V20"/>
-      <c r="W20"/>
       <c r="X20" t="s">
         <v>121</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="Y20">
         <v>1</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="Z20">
         <v>2</v>
       </c>
       <c r="AA20" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="n">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
@@ -3040,20 +2923,19 @@
       <c r="E21" t="s">
         <v>122</v>
       </c>
-      <c r="F21"/>
-      <c r="G21" t="n">
+      <c r="G21">
         <v>208984000000</v>
       </c>
       <c r="H21" t="s">
         <v>71</v>
       </c>
-      <c r="I21" t="n">
+      <c r="I21">
         <v>38961</v>
       </c>
       <c r="J21" t="s">
         <v>31</v>
       </c>
-      <c r="K21" t="n">
+      <c r="K21">
         <v>2.76</v>
       </c>
       <c r="L21" t="s">
@@ -3065,36 +2947,30 @@
       <c r="N21" t="s">
         <v>34</v>
       </c>
-      <c r="O21"/>
-      <c r="P21"/>
-      <c r="Q21" t="n">
+      <c r="Q21">
         <v>86.9</v>
       </c>
-      <c r="R21"/>
-      <c r="S21"/>
       <c r="T21" t="b">
         <v>0</v>
       </c>
       <c r="U21" t="s">
         <v>124</v>
       </c>
-      <c r="V21"/>
-      <c r="W21"/>
       <c r="X21" t="s">
         <v>125</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="Y21">
         <v>2</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="Z21">
         <v>2</v>
       </c>
       <c r="AA21" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="n">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
@@ -3109,21 +2985,20 @@
       <c r="E22" t="s">
         <v>126</v>
       </c>
-      <c r="F22"/>
-      <c r="G22" t="n">
+      <c r="G22">
         <v>208984000000</v>
       </c>
       <c r="H22" t="s">
         <v>76</v>
       </c>
-      <c r="I22" t="n">
+      <c r="I22">
         <v>39704</v>
       </c>
       <c r="J22" t="s">
         <v>31</v>
       </c>
-      <c r="K22" t="n">
-        <v>1.799</v>
+      <c r="K22">
+        <v>1.7989999999999999</v>
       </c>
       <c r="L22" t="s">
         <v>51</v>
@@ -3134,36 +3009,30 @@
       <c r="N22" t="s">
         <v>34</v>
       </c>
-      <c r="O22"/>
-      <c r="P22"/>
-      <c r="Q22" t="n">
+      <c r="Q22">
         <v>15</v>
       </c>
-      <c r="R22"/>
-      <c r="S22"/>
       <c r="T22" t="b">
         <v>0</v>
       </c>
       <c r="U22" t="s">
         <v>128</v>
       </c>
-      <c r="V22"/>
-      <c r="W22"/>
       <c r="X22" t="s">
         <v>129</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="Y22">
         <v>3</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="Z22">
         <v>2</v>
       </c>
       <c r="AA22" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="n">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
@@ -3178,21 +3047,20 @@
       <c r="E23" t="s">
         <v>130</v>
       </c>
-      <c r="F23"/>
-      <c r="G23" t="n">
+      <c r="G23">
         <v>208984000000</v>
       </c>
       <c r="H23" t="s">
         <v>81</v>
       </c>
-      <c r="I23" t="n">
+      <c r="I23">
         <v>40123</v>
       </c>
       <c r="J23" t="s">
         <v>31</v>
       </c>
-      <c r="K23" t="n">
-        <v>0.285</v>
+      <c r="K23">
+        <v>0.28499999999999998</v>
       </c>
       <c r="L23" t="s">
         <v>32</v>
@@ -3203,36 +3071,30 @@
       <c r="N23" t="s">
         <v>34</v>
       </c>
-      <c r="O23"/>
-      <c r="P23"/>
-      <c r="Q23" t="n">
+      <c r="Q23">
         <v>14.9</v>
       </c>
-      <c r="R23"/>
-      <c r="S23"/>
       <c r="T23" t="b">
         <v>0</v>
       </c>
       <c r="U23" t="s">
         <v>132</v>
       </c>
-      <c r="V23"/>
-      <c r="W23"/>
       <c r="X23" t="s">
         <v>133</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="Y23">
         <v>4</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="Z23">
         <v>2</v>
       </c>
       <c r="AA23" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="n">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
@@ -3247,20 +3109,19 @@
       <c r="E24" t="s">
         <v>134</v>
       </c>
-      <c r="F24"/>
-      <c r="G24" t="n">
+      <c r="G24">
         <v>208984000000</v>
       </c>
       <c r="H24" t="s">
         <v>86</v>
       </c>
-      <c r="I24" t="n">
+      <c r="I24">
         <v>39653</v>
       </c>
       <c r="J24" t="s">
         <v>31</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K24">
         <v>1.867214237</v>
       </c>
       <c r="L24" t="s">
@@ -3272,36 +3133,30 @@
       <c r="N24" t="s">
         <v>34</v>
       </c>
-      <c r="O24"/>
-      <c r="P24"/>
-      <c r="Q24" t="n">
+      <c r="Q24">
         <v>31.1</v>
       </c>
-      <c r="R24"/>
-      <c r="S24"/>
       <c r="T24" t="b">
         <v>0</v>
       </c>
       <c r="U24" t="s">
         <v>136</v>
       </c>
-      <c r="V24"/>
-      <c r="W24"/>
       <c r="X24" t="s">
         <v>137</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="Y24">
         <v>5</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="Z24">
         <v>2</v>
       </c>
       <c r="AA24" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="n">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A25">
         <v>24</v>
       </c>
       <c r="B25" t="s">
@@ -3316,20 +3171,19 @@
       <c r="E25" t="s">
         <v>138</v>
       </c>
-      <c r="F25"/>
-      <c r="G25" t="n">
+      <c r="G25">
         <v>208984000000</v>
       </c>
       <c r="H25" t="s">
         <v>91</v>
       </c>
-      <c r="I25" t="n">
+      <c r="I25">
         <v>39727</v>
       </c>
       <c r="J25" t="s">
         <v>31</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K25">
         <v>1.744</v>
       </c>
       <c r="L25" t="s">
@@ -3341,36 +3195,30 @@
       <c r="N25" t="s">
         <v>34</v>
       </c>
-      <c r="O25"/>
-      <c r="P25"/>
-      <c r="Q25" t="n">
+      <c r="Q25">
         <v>20.6</v>
       </c>
-      <c r="R25"/>
-      <c r="S25"/>
       <c r="T25" t="b">
         <v>0</v>
       </c>
       <c r="U25" t="s">
         <v>140</v>
       </c>
-      <c r="V25"/>
-      <c r="W25"/>
       <c r="X25" t="s">
         <v>141</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="Y25">
         <v>6</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="Z25">
         <v>2</v>
       </c>
       <c r="AA25" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="n">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A26">
         <v>25</v>
       </c>
       <c r="B26" t="s">
@@ -3385,21 +3233,20 @@
       <c r="E26" t="s">
         <v>142</v>
       </c>
-      <c r="F26"/>
-      <c r="G26" t="n">
+      <c r="G26">
         <v>208984000000</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I26">
         <v>39960</v>
       </c>
       <c r="J26" t="s">
         <v>31</v>
       </c>
-      <c r="K26" t="n">
-        <v>1.257</v>
+      <c r="K26">
+        <v>1.2569999999999999</v>
       </c>
       <c r="L26" t="s">
         <v>51</v>
@@ -3410,36 +3257,30 @@
       <c r="N26" t="s">
         <v>34</v>
       </c>
-      <c r="O26"/>
-      <c r="P26"/>
-      <c r="Q26" t="n">
+      <c r="Q26">
         <v>18.7</v>
       </c>
-      <c r="R26"/>
-      <c r="S26"/>
       <c r="T26" t="b">
         <v>0</v>
       </c>
       <c r="U26" t="s">
         <v>144</v>
       </c>
-      <c r="V26"/>
-      <c r="W26"/>
       <c r="X26" t="s">
         <v>145</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="Y26">
         <v>1</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="Z26">
         <v>1</v>
       </c>
       <c r="AA26" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="n">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A27">
         <v>26</v>
       </c>
       <c r="B27" t="s">
@@ -3454,21 +3295,20 @@
       <c r="E27" t="s">
         <v>146</v>
       </c>
-      <c r="F27"/>
-      <c r="G27" t="n">
+      <c r="G27">
         <v>208984000000</v>
       </c>
       <c r="H27" t="s">
         <v>40</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I27">
         <v>40126</v>
       </c>
       <c r="J27" t="s">
         <v>31</v>
       </c>
-      <c r="K27" t="n">
-        <v>0.285</v>
+      <c r="K27">
+        <v>0.28499999999999998</v>
       </c>
       <c r="L27" t="s">
         <v>32</v>
@@ -3479,36 +3319,30 @@
       <c r="N27" t="s">
         <v>34</v>
       </c>
-      <c r="O27"/>
-      <c r="P27"/>
-      <c r="Q27" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R27"/>
-      <c r="S27"/>
+      <c r="Q27">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T27" t="b">
         <v>0</v>
       </c>
       <c r="U27" t="s">
         <v>148</v>
       </c>
-      <c r="V27"/>
-      <c r="W27"/>
       <c r="X27" t="s">
         <v>149</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="Y27">
         <v>2</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="Z27">
         <v>1</v>
       </c>
       <c r="AA27" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="n">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A28">
         <v>27</v>
       </c>
       <c r="B28" t="s">
@@ -3523,21 +3357,20 @@
       <c r="E28" t="s">
         <v>150</v>
       </c>
-      <c r="F28"/>
-      <c r="G28" t="n">
+      <c r="G28">
         <v>208984000000</v>
       </c>
       <c r="H28" t="s">
         <v>45</v>
       </c>
-      <c r="I28" t="n">
+      <c r="I28">
         <v>40063</v>
       </c>
       <c r="J28" t="s">
         <v>31</v>
       </c>
-      <c r="K28" t="n">
-        <v>0.493</v>
+      <c r="K28">
+        <v>0.49299999999999999</v>
       </c>
       <c r="L28" t="s">
         <v>32</v>
@@ -3548,36 +3381,30 @@
       <c r="N28" t="s">
         <v>34</v>
       </c>
-      <c r="O28"/>
-      <c r="P28"/>
-      <c r="Q28" t="n">
+      <c r="Q28">
         <v>14.9</v>
       </c>
-      <c r="R28"/>
-      <c r="S28"/>
       <c r="T28" t="b">
         <v>0</v>
       </c>
       <c r="U28" t="s">
         <v>152</v>
       </c>
-      <c r="V28"/>
-      <c r="W28"/>
       <c r="X28" t="s">
         <v>153</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="Y28">
         <v>3</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="Z28">
         <v>1</v>
       </c>
       <c r="AA28" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="n">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A29">
         <v>28</v>
       </c>
       <c r="B29" t="s">
@@ -3592,21 +3419,20 @@
       <c r="E29" t="s">
         <v>154</v>
       </c>
-      <c r="F29"/>
-      <c r="G29" t="n">
+      <c r="G29">
         <v>208984000000</v>
       </c>
       <c r="H29" t="s">
         <v>50</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I29">
         <v>39707</v>
       </c>
       <c r="J29" t="s">
         <v>31</v>
       </c>
-      <c r="K29" t="n">
-        <v>1.769</v>
+      <c r="K29">
+        <v>1.7689999999999999</v>
       </c>
       <c r="L29" t="s">
         <v>32</v>
@@ -3617,36 +3443,30 @@
       <c r="N29" t="s">
         <v>34</v>
       </c>
-      <c r="O29"/>
-      <c r="P29"/>
-      <c r="Q29" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R29"/>
-      <c r="S29"/>
+      <c r="Q29">
+        <v>19.600000000000001</v>
+      </c>
       <c r="T29" t="b">
         <v>0</v>
       </c>
       <c r="U29" t="s">
         <v>156</v>
       </c>
-      <c r="V29"/>
-      <c r="W29"/>
       <c r="X29" t="s">
         <v>157</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y29">
         <v>4</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="Z29">
         <v>1</v>
       </c>
       <c r="AA29" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="n">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A30">
         <v>29</v>
       </c>
       <c r="B30" t="s">
@@ -3661,21 +3481,20 @@
       <c r="E30" t="s">
         <v>158</v>
       </c>
-      <c r="F30"/>
-      <c r="G30" t="n">
+      <c r="G30">
         <v>208984000000</v>
       </c>
       <c r="H30" t="s">
         <v>56</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I30">
         <v>40116</v>
       </c>
       <c r="J30" t="s">
         <v>31</v>
       </c>
-      <c r="K30" t="n">
-        <v>0.34770705</v>
+      <c r="K30">
+        <v>0.34770705000000002</v>
       </c>
       <c r="L30" t="s">
         <v>51</v>
@@ -3686,36 +3505,30 @@
       <c r="N30" t="s">
         <v>34</v>
       </c>
-      <c r="O30"/>
-      <c r="P30"/>
-      <c r="Q30" t="n">
+      <c r="Q30">
         <v>26.4</v>
       </c>
-      <c r="R30"/>
-      <c r="S30"/>
       <c r="T30" t="b">
         <v>0</v>
       </c>
       <c r="U30" t="s">
         <v>160</v>
       </c>
-      <c r="V30"/>
-      <c r="W30"/>
       <c r="X30" t="s">
         <v>161</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Y30">
         <v>5</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="Z30">
         <v>1</v>
       </c>
       <c r="AA30" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="n">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A31">
         <v>30</v>
       </c>
       <c r="B31" t="s">
@@ -3730,21 +3543,20 @@
       <c r="E31" t="s">
         <v>162</v>
       </c>
-      <c r="F31"/>
-      <c r="G31" t="n">
+      <c r="G31">
         <v>208984000000</v>
       </c>
       <c r="H31" t="s">
         <v>61</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I31">
         <v>40039</v>
       </c>
       <c r="J31" t="s">
         <v>31</v>
       </c>
-      <c r="K31" t="n">
-        <v>0.742</v>
+      <c r="K31">
+        <v>0.74199999999999999</v>
       </c>
       <c r="L31" t="s">
         <v>51</v>
@@ -3755,36 +3567,30 @@
       <c r="N31" t="s">
         <v>34</v>
       </c>
-      <c r="O31"/>
-      <c r="P31"/>
-      <c r="Q31" t="n">
+      <c r="Q31">
         <v>15.6</v>
       </c>
-      <c r="R31"/>
-      <c r="S31"/>
       <c r="T31" t="b">
         <v>0</v>
       </c>
       <c r="U31" t="s">
         <v>164</v>
       </c>
-      <c r="V31"/>
-      <c r="W31"/>
       <c r="X31" t="s">
         <v>165</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Y31">
         <v>6</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="Z31">
         <v>1</v>
       </c>
       <c r="AA31" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="n">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>31</v>
       </c>
       <c r="B32" t="s">
@@ -3799,21 +3605,20 @@
       <c r="E32" t="s">
         <v>166</v>
       </c>
-      <c r="F32"/>
-      <c r="G32" t="n">
+      <c r="G32">
         <v>208984000000</v>
       </c>
       <c r="H32" t="s">
         <v>66</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I32">
         <v>39688</v>
       </c>
       <c r="J32" t="s">
         <v>31</v>
       </c>
-      <c r="K32" t="n">
-        <v>1.793</v>
+      <c r="K32">
+        <v>1.7929999999999999</v>
       </c>
       <c r="L32" t="s">
         <v>51</v>
@@ -3824,36 +3629,30 @@
       <c r="N32" t="s">
         <v>34</v>
       </c>
-      <c r="O32"/>
-      <c r="P32"/>
-      <c r="Q32" t="n">
+      <c r="Q32">
         <v>15.9</v>
       </c>
-      <c r="R32"/>
-      <c r="S32"/>
       <c r="T32" t="b">
         <v>0</v>
       </c>
       <c r="U32" t="s">
         <v>168</v>
       </c>
-      <c r="V32"/>
-      <c r="W32"/>
       <c r="X32" t="s">
         <v>169</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Y32">
         <v>1</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="Z32">
         <v>2</v>
       </c>
       <c r="AA32" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="n">
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A33">
         <v>32</v>
       </c>
       <c r="B33" t="s">
@@ -3868,21 +3667,20 @@
       <c r="E33" t="s">
         <v>170</v>
       </c>
-      <c r="F33"/>
-      <c r="G33" t="n">
+      <c r="G33">
         <v>208984000000</v>
       </c>
       <c r="H33" t="s">
         <v>71</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I33">
         <v>39882</v>
       </c>
       <c r="J33" t="s">
         <v>31</v>
       </c>
-      <c r="K33" t="n">
-        <v>1.511</v>
+      <c r="K33">
+        <v>1.5109999999999999</v>
       </c>
       <c r="L33" t="s">
         <v>32</v>
@@ -3893,36 +3691,30 @@
       <c r="N33" t="s">
         <v>34</v>
       </c>
-      <c r="O33"/>
-      <c r="P33"/>
-      <c r="Q33" t="n">
+      <c r="Q33">
         <v>23.8</v>
       </c>
-      <c r="R33"/>
-      <c r="S33"/>
       <c r="T33" t="b">
         <v>0</v>
       </c>
       <c r="U33" t="s">
         <v>172</v>
       </c>
-      <c r="V33"/>
-      <c r="W33"/>
       <c r="X33" t="s">
         <v>173</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Y33">
         <v>2</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="Z33">
         <v>2</v>
       </c>
       <c r="AA33" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="n">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A34">
         <v>33</v>
       </c>
       <c r="B34" t="s">
@@ -3937,20 +3729,19 @@
       <c r="E34" t="s">
         <v>174</v>
       </c>
-      <c r="F34"/>
-      <c r="G34" t="n">
+      <c r="G34">
         <v>208984000000</v>
       </c>
       <c r="H34" t="s">
         <v>76</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I34">
         <v>39658</v>
       </c>
       <c r="J34" t="s">
         <v>31</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K34">
         <v>1.869952088</v>
       </c>
       <c r="L34" t="s">
@@ -3962,36 +3753,30 @@
       <c r="N34" t="s">
         <v>34</v>
       </c>
-      <c r="O34"/>
-      <c r="P34"/>
-      <c r="Q34" t="n">
+      <c r="Q34">
         <v>33.4</v>
       </c>
-      <c r="R34"/>
-      <c r="S34"/>
       <c r="T34" t="b">
         <v>0</v>
       </c>
       <c r="U34" t="s">
         <v>176</v>
       </c>
-      <c r="V34"/>
-      <c r="W34"/>
       <c r="X34" t="s">
         <v>177</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Y34">
         <v>3</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="Z34">
         <v>2</v>
       </c>
       <c r="AA34" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="n">
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A35">
         <v>34</v>
       </c>
       <c r="B35" t="s">
@@ -4006,21 +3791,20 @@
       <c r="E35" t="s">
         <v>178</v>
       </c>
-      <c r="F35"/>
-      <c r="G35" t="n">
+      <c r="G35">
         <v>208984000000</v>
       </c>
       <c r="H35" t="s">
         <v>81</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I35">
         <v>39768</v>
       </c>
       <c r="J35" t="s">
         <v>31</v>
       </c>
-      <c r="K35" t="n">
-        <v>1.703</v>
+      <c r="K35">
+        <v>1.7030000000000001</v>
       </c>
       <c r="L35" t="s">
         <v>32</v>
@@ -4031,36 +3815,30 @@
       <c r="N35" t="s">
         <v>34</v>
       </c>
-      <c r="O35"/>
-      <c r="P35"/>
-      <c r="Q35" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R35"/>
-      <c r="S35"/>
+      <c r="Q35">
+        <v>19.600000000000001</v>
+      </c>
       <c r="T35" t="b">
         <v>0</v>
       </c>
       <c r="U35" t="s">
         <v>180</v>
       </c>
-      <c r="V35"/>
-      <c r="W35"/>
       <c r="X35" t="s">
         <v>181</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y35">
         <v>4</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="Z35">
         <v>2</v>
       </c>
       <c r="AA35" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="n">
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A36">
         <v>35</v>
       </c>
       <c r="B36" t="s">
@@ -4075,21 +3853,20 @@
       <c r="E36" t="s">
         <v>182</v>
       </c>
-      <c r="F36"/>
-      <c r="G36" t="n">
+      <c r="G36">
         <v>208984000000</v>
       </c>
       <c r="H36" t="s">
         <v>86</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I36">
         <v>40085</v>
       </c>
       <c r="J36" t="s">
         <v>31</v>
       </c>
-      <c r="K36" t="n">
-        <v>0.381</v>
+      <c r="K36">
+        <v>0.38100000000000001</v>
       </c>
       <c r="L36" t="s">
         <v>51</v>
@@ -4100,36 +3877,30 @@
       <c r="N36" t="s">
         <v>34</v>
       </c>
-      <c r="O36"/>
-      <c r="P36"/>
-      <c r="Q36" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="R36"/>
-      <c r="S36"/>
+      <c r="Q36">
+        <v>18.600000000000001</v>
+      </c>
       <c r="T36" t="b">
         <v>0</v>
       </c>
       <c r="U36" t="s">
         <v>184</v>
       </c>
-      <c r="V36"/>
-      <c r="W36"/>
       <c r="X36" t="s">
         <v>185</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Y36">
         <v>5</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="Z36">
         <v>2</v>
       </c>
       <c r="AA36" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="n">
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A37">
         <v>36</v>
       </c>
       <c r="B37" t="s">
@@ -4144,20 +3915,19 @@
       <c r="E37" t="s">
         <v>186</v>
       </c>
-      <c r="F37"/>
-      <c r="G37" t="n">
+      <c r="G37">
         <v>208984000000</v>
       </c>
       <c r="H37" t="s">
         <v>91</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I37">
         <v>39990</v>
       </c>
       <c r="J37" t="s">
         <v>31</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K37">
         <v>1.169</v>
       </c>
       <c r="L37" t="s">
@@ -4169,36 +3939,30 @@
       <c r="N37" t="s">
         <v>34</v>
       </c>
-      <c r="O37"/>
-      <c r="P37"/>
-      <c r="Q37" t="n">
+      <c r="Q37">
         <v>41.4</v>
       </c>
-      <c r="R37"/>
-      <c r="S37"/>
       <c r="T37" t="b">
         <v>0</v>
       </c>
       <c r="U37" t="s">
         <v>188</v>
       </c>
-      <c r="V37"/>
-      <c r="W37"/>
       <c r="X37" t="s">
         <v>189</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y37">
         <v>6</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="Z37">
         <v>2</v>
       </c>
       <c r="AA37" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="n">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A38">
         <v>37</v>
       </c>
       <c r="B38" t="s">
@@ -4213,21 +3977,20 @@
       <c r="E38" t="s">
         <v>190</v>
       </c>
-      <c r="F38"/>
-      <c r="G38" t="n">
+      <c r="G38">
         <v>208984000000</v>
       </c>
       <c r="H38" t="s">
         <v>30</v>
       </c>
-      <c r="I38" t="n">
+      <c r="I38">
         <v>40072</v>
       </c>
       <c r="J38" t="s">
         <v>31</v>
       </c>
-      <c r="K38" t="n">
-        <v>0.424</v>
+      <c r="K38">
+        <v>0.42399999999999999</v>
       </c>
       <c r="L38" t="s">
         <v>32</v>
@@ -4238,36 +4001,30 @@
       <c r="N38" t="s">
         <v>34</v>
       </c>
-      <c r="O38"/>
-      <c r="P38"/>
-      <c r="Q38" t="n">
+      <c r="Q38">
         <v>14.9</v>
       </c>
-      <c r="R38"/>
-      <c r="S38"/>
       <c r="T38" t="b">
         <v>0</v>
       </c>
       <c r="U38" t="s">
         <v>192</v>
       </c>
-      <c r="V38"/>
-      <c r="W38"/>
       <c r="X38" t="s">
         <v>193</v>
       </c>
-      <c r="Y38" t="n">
+      <c r="Y38">
         <v>1</v>
       </c>
-      <c r="Z38" t="n">
+      <c r="Z38">
         <v>1</v>
       </c>
       <c r="AA38" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="n">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A39">
         <v>38</v>
       </c>
       <c r="B39" t="s">
@@ -4282,20 +4039,19 @@
       <c r="E39" t="s">
         <v>194</v>
       </c>
-      <c r="F39"/>
-      <c r="G39" t="n">
+      <c r="G39">
         <v>208984000000</v>
       </c>
       <c r="H39" t="s">
         <v>40</v>
       </c>
-      <c r="I39" t="n">
+      <c r="I39">
         <v>40143</v>
       </c>
       <c r="J39" t="s">
         <v>31</v>
       </c>
-      <c r="K39" t="n">
+      <c r="K39">
         <v>0.23</v>
       </c>
       <c r="L39" t="s">
@@ -4307,36 +4063,30 @@
       <c r="N39" t="s">
         <v>34</v>
       </c>
-      <c r="O39"/>
-      <c r="P39"/>
-      <c r="Q39" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="R39"/>
-      <c r="S39"/>
+      <c r="Q39">
+        <v>18.600000000000001</v>
+      </c>
       <c r="T39" t="b">
         <v>0</v>
       </c>
       <c r="U39" t="s">
         <v>196</v>
       </c>
-      <c r="V39"/>
-      <c r="W39"/>
       <c r="X39" t="s">
         <v>197</v>
       </c>
-      <c r="Y39" t="n">
+      <c r="Y39">
         <v>2</v>
       </c>
-      <c r="Z39" t="n">
+      <c r="Z39">
         <v>1</v>
       </c>
       <c r="AA39" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="n">
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A40">
         <v>39</v>
       </c>
       <c r="B40" t="s">
@@ -4351,21 +4101,20 @@
       <c r="E40" t="s">
         <v>198</v>
       </c>
-      <c r="F40"/>
-      <c r="G40" t="n">
+      <c r="G40">
         <v>208984000000</v>
       </c>
       <c r="H40" t="s">
         <v>45</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I40">
         <v>40096</v>
       </c>
       <c r="J40" t="s">
         <v>31</v>
       </c>
-      <c r="K40" t="n">
-        <v>0.356</v>
+      <c r="K40">
+        <v>0.35599999999999998</v>
       </c>
       <c r="L40" t="s">
         <v>32</v>
@@ -4376,36 +4125,30 @@
       <c r="N40" t="s">
         <v>34</v>
       </c>
-      <c r="O40"/>
-      <c r="P40"/>
-      <c r="Q40" t="n">
+      <c r="Q40">
         <v>14.9</v>
       </c>
-      <c r="R40"/>
-      <c r="S40"/>
       <c r="T40" t="b">
         <v>0</v>
       </c>
       <c r="U40" t="s">
         <v>200</v>
       </c>
-      <c r="V40"/>
-      <c r="W40"/>
       <c r="X40" t="s">
         <v>201</v>
       </c>
-      <c r="Y40" t="n">
+      <c r="Y40">
         <v>3</v>
       </c>
-      <c r="Z40" t="n">
+      <c r="Z40">
         <v>1</v>
       </c>
       <c r="AA40" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="n">
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A41">
         <v>40</v>
       </c>
       <c r="B41" t="s">
@@ -4420,20 +4163,19 @@
       <c r="E41" t="s">
         <v>202</v>
       </c>
-      <c r="F41"/>
-      <c r="G41" t="n">
+      <c r="G41">
         <v>208984000000</v>
       </c>
       <c r="H41" t="s">
         <v>50</v>
       </c>
-      <c r="I41" t="n">
+      <c r="I41">
         <v>39836</v>
       </c>
       <c r="J41" t="s">
         <v>31</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K41">
         <v>1.591</v>
       </c>
       <c r="L41" t="s">
@@ -4445,36 +4187,30 @@
       <c r="N41" t="s">
         <v>34</v>
       </c>
-      <c r="O41"/>
-      <c r="P41"/>
-      <c r="Q41" t="n">
+      <c r="Q41">
         <v>34.4</v>
       </c>
-      <c r="R41"/>
-      <c r="S41"/>
       <c r="T41" t="b">
         <v>0</v>
       </c>
       <c r="U41" t="s">
         <v>204</v>
       </c>
-      <c r="V41"/>
-      <c r="W41"/>
       <c r="X41" t="s">
         <v>205</v>
       </c>
-      <c r="Y41" t="n">
+      <c r="Y41">
         <v>4</v>
       </c>
-      <c r="Z41" t="n">
+      <c r="Z41">
         <v>1</v>
       </c>
       <c r="AA41" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="n">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A42">
         <v>41</v>
       </c>
       <c r="B42" t="s">
@@ -4489,20 +4225,19 @@
       <c r="E42" t="s">
         <v>206</v>
       </c>
-      <c r="F42"/>
-      <c r="G42" t="n">
+      <c r="G42">
         <v>208984000000</v>
       </c>
       <c r="H42" t="s">
         <v>56</v>
       </c>
-      <c r="I42" t="n">
+      <c r="I42">
         <v>40194</v>
       </c>
       <c r="J42" t="s">
         <v>31</v>
       </c>
-      <c r="K42" t="n">
+      <c r="K42">
         <v>0.114989733</v>
       </c>
       <c r="L42" t="s">
@@ -4514,36 +4249,30 @@
       <c r="N42" t="s">
         <v>34</v>
       </c>
-      <c r="O42"/>
-      <c r="P42"/>
-      <c r="Q42" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R42"/>
-      <c r="S42"/>
+      <c r="Q42">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T42" t="b">
         <v>0</v>
       </c>
       <c r="U42" t="s">
         <v>208</v>
       </c>
-      <c r="V42"/>
-      <c r="W42"/>
       <c r="X42" t="s">
         <v>209</v>
       </c>
-      <c r="Y42" t="n">
+      <c r="Y42">
         <v>5</v>
       </c>
-      <c r="Z42" t="n">
+      <c r="Z42">
         <v>1</v>
       </c>
       <c r="AA42" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="n">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A43">
         <v>42</v>
       </c>
       <c r="B43" t="s">
@@ -4558,20 +4287,19 @@
       <c r="E43" t="s">
         <v>210</v>
       </c>
-      <c r="F43"/>
-      <c r="G43" t="n">
+      <c r="G43">
         <v>208984000000</v>
       </c>
       <c r="H43" t="s">
         <v>61</v>
       </c>
-      <c r="I43" t="n">
+      <c r="I43">
         <v>40145</v>
       </c>
       <c r="J43" t="s">
         <v>31</v>
       </c>
-      <c r="K43" t="n">
+      <c r="K43">
         <v>0.216</v>
       </c>
       <c r="L43" t="s">
@@ -4583,36 +4311,30 @@
       <c r="N43" t="s">
         <v>34</v>
       </c>
-      <c r="O43"/>
-      <c r="P43"/>
-      <c r="Q43" t="n">
+      <c r="Q43">
         <v>14.9</v>
       </c>
-      <c r="R43"/>
-      <c r="S43"/>
       <c r="T43" t="b">
         <v>0</v>
       </c>
       <c r="U43" t="s">
         <v>212</v>
       </c>
-      <c r="V43"/>
-      <c r="W43"/>
       <c r="X43" t="s">
         <v>213</v>
       </c>
-      <c r="Y43" t="n">
+      <c r="Y43">
         <v>6</v>
       </c>
-      <c r="Z43" t="n">
+      <c r="Z43">
         <v>1</v>
       </c>
       <c r="AA43" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A44">
         <v>43</v>
       </c>
       <c r="B44" t="s">
@@ -4627,21 +4349,20 @@
       <c r="E44" t="s">
         <v>214</v>
       </c>
-      <c r="F44"/>
-      <c r="G44" t="n">
+      <c r="G44">
         <v>208984000000</v>
       </c>
       <c r="H44" t="s">
         <v>66</v>
       </c>
-      <c r="I44" t="n">
+      <c r="I44">
         <v>39785</v>
       </c>
       <c r="J44" t="s">
         <v>31</v>
       </c>
-      <c r="K44" t="n">
-        <v>1.654</v>
+      <c r="K44">
+        <v>1.6539999999999999</v>
       </c>
       <c r="L44" t="s">
         <v>32</v>
@@ -4652,36 +4373,30 @@
       <c r="N44" t="s">
         <v>34</v>
       </c>
-      <c r="O44"/>
-      <c r="P44"/>
-      <c r="Q44" t="n">
+      <c r="Q44">
         <v>23.8</v>
       </c>
-      <c r="R44"/>
-      <c r="S44"/>
       <c r="T44" t="b">
         <v>0</v>
       </c>
       <c r="U44" t="s">
         <v>216</v>
       </c>
-      <c r="V44"/>
-      <c r="W44"/>
       <c r="X44" t="s">
         <v>217</v>
       </c>
-      <c r="Y44" t="n">
+      <c r="Y44">
         <v>1</v>
       </c>
-      <c r="Z44" t="n">
+      <c r="Z44">
         <v>2</v>
       </c>
       <c r="AA44" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="n">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A45">
         <v>44</v>
       </c>
       <c r="B45" t="s">
@@ -4696,21 +4411,20 @@
       <c r="E45" t="s">
         <v>218</v>
       </c>
-      <c r="F45"/>
-      <c r="G45" t="n">
+      <c r="G45">
         <v>208984000000</v>
       </c>
       <c r="H45" t="s">
         <v>71</v>
       </c>
-      <c r="I45" t="n">
+      <c r="I45">
         <v>40083</v>
       </c>
       <c r="J45" t="s">
         <v>31</v>
       </c>
-      <c r="K45" t="n">
-        <v>0.381</v>
+      <c r="K45">
+        <v>0.38100000000000001</v>
       </c>
       <c r="L45" t="s">
         <v>51</v>
@@ -4721,36 +4435,30 @@
       <c r="N45" t="s">
         <v>34</v>
       </c>
-      <c r="O45"/>
-      <c r="P45"/>
-      <c r="Q45" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="R45"/>
-      <c r="S45"/>
+      <c r="Q45">
+        <v>18.600000000000001</v>
+      </c>
       <c r="T45" t="b">
         <v>0</v>
       </c>
       <c r="U45" t="s">
         <v>220</v>
       </c>
-      <c r="V45"/>
-      <c r="W45"/>
       <c r="X45" t="s">
         <v>221</v>
       </c>
-      <c r="Y45" t="n">
+      <c r="Y45">
         <v>2</v>
       </c>
-      <c r="Z45" t="n">
+      <c r="Z45">
         <v>2</v>
       </c>
       <c r="AA45" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A46">
         <v>45</v>
       </c>
       <c r="B46" t="s">
@@ -4765,21 +4473,20 @@
       <c r="E46" t="s">
         <v>222</v>
       </c>
-      <c r="F46"/>
-      <c r="G46" t="n">
+      <c r="G46">
         <v>208984000000</v>
       </c>
       <c r="H46" t="s">
         <v>76</v>
       </c>
-      <c r="I46" t="n">
+      <c r="I46">
         <v>40066</v>
       </c>
       <c r="J46" t="s">
         <v>31</v>
       </c>
-      <c r="K46" t="n">
-        <v>0.474</v>
+      <c r="K46">
+        <v>0.47399999999999998</v>
       </c>
       <c r="L46" t="s">
         <v>51</v>
@@ -4790,36 +4497,30 @@
       <c r="N46" t="s">
         <v>34</v>
       </c>
-      <c r="O46"/>
-      <c r="P46"/>
-      <c r="Q46" t="n">
+      <c r="Q46">
         <v>19.3</v>
       </c>
-      <c r="R46"/>
-      <c r="S46"/>
       <c r="T46" t="b">
         <v>0</v>
       </c>
       <c r="U46" t="s">
         <v>224</v>
       </c>
-      <c r="V46"/>
-      <c r="W46"/>
       <c r="X46" t="s">
         <v>225</v>
       </c>
-      <c r="Y46" t="n">
+      <c r="Y46">
         <v>3</v>
       </c>
-      <c r="Z46" t="n">
+      <c r="Z46">
         <v>2</v>
       </c>
       <c r="AA46" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="n">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A47">
         <v>46</v>
       </c>
       <c r="B47" t="s">
@@ -4834,20 +4535,19 @@
       <c r="E47" t="s">
         <v>226</v>
       </c>
-      <c r="F47"/>
-      <c r="G47" t="n">
+      <c r="G47">
         <v>208984000000</v>
       </c>
       <c r="H47" t="s">
         <v>81</v>
       </c>
-      <c r="I47" t="n">
+      <c r="I47">
         <v>40150</v>
       </c>
       <c r="J47" t="s">
         <v>31</v>
       </c>
-      <c r="K47" t="n">
+      <c r="K47">
         <v>0.216</v>
       </c>
       <c r="L47" t="s">
@@ -4859,36 +4559,30 @@
       <c r="N47" t="s">
         <v>34</v>
       </c>
-      <c r="O47"/>
-      <c r="P47"/>
-      <c r="Q47" t="n">
+      <c r="Q47">
         <v>20.8</v>
       </c>
-      <c r="R47"/>
-      <c r="S47"/>
       <c r="T47" t="b">
         <v>0</v>
       </c>
       <c r="U47" t="s">
         <v>228</v>
       </c>
-      <c r="V47"/>
-      <c r="W47"/>
       <c r="X47" t="s">
         <v>229</v>
       </c>
-      <c r="Y47" t="n">
+      <c r="Y47">
         <v>4</v>
       </c>
-      <c r="Z47" t="n">
+      <c r="Z47">
         <v>2</v>
       </c>
       <c r="AA47" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="n">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A48">
         <v>47</v>
       </c>
       <c r="B48" t="s">
@@ -4903,21 +4597,20 @@
       <c r="E48" t="s">
         <v>230</v>
       </c>
-      <c r="F48"/>
-      <c r="G48" t="n">
+      <c r="G48">
         <v>208984000000</v>
       </c>
       <c r="H48" t="s">
         <v>86</v>
       </c>
-      <c r="I48" t="n">
+      <c r="I48">
         <v>40060</v>
       </c>
       <c r="J48" t="s">
         <v>31</v>
       </c>
-      <c r="K48" t="n">
-        <v>0.493</v>
+      <c r="K48">
+        <v>0.49299999999999999</v>
       </c>
       <c r="L48" t="s">
         <v>32</v>
@@ -4928,36 +4621,30 @@
       <c r="N48" t="s">
         <v>34</v>
       </c>
-      <c r="O48"/>
-      <c r="P48"/>
-      <c r="Q48" t="n">
+      <c r="Q48">
         <v>14.9</v>
       </c>
-      <c r="R48"/>
-      <c r="S48"/>
       <c r="T48" t="b">
         <v>0</v>
       </c>
       <c r="U48" t="s">
         <v>232</v>
       </c>
-      <c r="V48"/>
-      <c r="W48"/>
       <c r="X48" t="s">
         <v>233</v>
       </c>
-      <c r="Y48" t="n">
+      <c r="Y48">
         <v>5</v>
       </c>
-      <c r="Z48" t="n">
+      <c r="Z48">
         <v>2</v>
       </c>
       <c r="AA48" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="n">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A49">
         <v>48</v>
       </c>
       <c r="B49" t="s">
@@ -4972,21 +4659,20 @@
       <c r="E49" t="s">
         <v>234</v>
       </c>
-      <c r="F49"/>
-      <c r="G49" t="n">
+      <c r="G49">
         <v>208984000000</v>
       </c>
       <c r="H49" t="s">
         <v>91</v>
       </c>
-      <c r="I49" t="n">
+      <c r="I49">
         <v>39692</v>
       </c>
       <c r="J49" t="s">
         <v>31</v>
       </c>
-      <c r="K49" t="n">
-        <v>1.807</v>
+      <c r="K49">
+        <v>1.8069999999999999</v>
       </c>
       <c r="L49" t="s">
         <v>51</v>
@@ -4997,36 +4683,30 @@
       <c r="N49" t="s">
         <v>34</v>
       </c>
-      <c r="O49"/>
-      <c r="P49"/>
-      <c r="Q49" t="n">
+      <c r="Q49">
         <v>20.6</v>
       </c>
-      <c r="R49"/>
-      <c r="S49"/>
       <c r="T49" t="b">
         <v>0</v>
       </c>
       <c r="U49" t="s">
         <v>236</v>
       </c>
-      <c r="V49"/>
-      <c r="W49"/>
       <c r="X49" t="s">
         <v>237</v>
       </c>
-      <c r="Y49" t="n">
+      <c r="Y49">
         <v>6</v>
       </c>
-      <c r="Z49" t="n">
+      <c r="Z49">
         <v>2</v>
       </c>
       <c r="AA49" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="n">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A50">
         <v>49</v>
       </c>
       <c r="B50" t="s">
@@ -5041,21 +4721,20 @@
       <c r="E50" t="s">
         <v>238</v>
       </c>
-      <c r="F50"/>
-      <c r="G50" t="n">
+      <c r="G50">
         <v>208984000000</v>
       </c>
       <c r="H50" t="s">
         <v>30</v>
       </c>
-      <c r="I50" t="n">
+      <c r="I50">
         <v>39644</v>
       </c>
       <c r="J50" t="s">
         <v>31</v>
       </c>
-      <c r="K50" t="n">
-        <v>1.862</v>
+      <c r="K50">
+        <v>1.8620000000000001</v>
       </c>
       <c r="L50" t="s">
         <v>51</v>
@@ -5066,36 +4745,30 @@
       <c r="N50" t="s">
         <v>34</v>
       </c>
-      <c r="O50"/>
-      <c r="P50"/>
-      <c r="Q50" t="n">
+      <c r="Q50">
         <v>20</v>
       </c>
-      <c r="R50"/>
-      <c r="S50"/>
       <c r="T50" t="b">
         <v>0</v>
       </c>
       <c r="U50" t="s">
         <v>240</v>
       </c>
-      <c r="V50"/>
-      <c r="W50"/>
       <c r="X50" t="s">
         <v>241</v>
       </c>
-      <c r="Y50" t="n">
+      <c r="Y50">
         <v>1</v>
       </c>
-      <c r="Z50" t="n">
+      <c r="Z50">
         <v>1</v>
       </c>
       <c r="AA50" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" t="n">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A51">
         <v>50</v>
       </c>
       <c r="B51" t="s">
@@ -5110,20 +4783,19 @@
       <c r="E51" t="s">
         <v>242</v>
       </c>
-      <c r="F51"/>
-      <c r="G51" t="n">
+      <c r="G51">
         <v>208984000000</v>
       </c>
       <c r="H51" t="s">
         <v>40</v>
       </c>
-      <c r="I51" t="n">
+      <c r="I51">
         <v>39838</v>
       </c>
       <c r="J51" t="s">
         <v>31</v>
       </c>
-      <c r="K51" t="n">
+      <c r="K51">
         <v>1.591</v>
       </c>
       <c r="L51" t="s">
@@ -5135,36 +4807,30 @@
       <c r="N51" t="s">
         <v>34</v>
       </c>
-      <c r="O51"/>
-      <c r="P51"/>
-      <c r="Q51" t="n">
+      <c r="Q51">
         <v>34.4</v>
       </c>
-      <c r="R51"/>
-      <c r="S51"/>
       <c r="T51" t="b">
         <v>0</v>
       </c>
       <c r="U51" t="s">
         <v>244</v>
       </c>
-      <c r="V51"/>
-      <c r="W51"/>
       <c r="X51" t="s">
         <v>245</v>
       </c>
-      <c r="Y51" t="n">
+      <c r="Y51">
         <v>2</v>
       </c>
-      <c r="Z51" t="n">
+      <c r="Z51">
         <v>1</v>
       </c>
       <c r="AA51" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" t="n">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" t="s">
@@ -5179,21 +4845,20 @@
       <c r="E52" t="s">
         <v>246</v>
       </c>
-      <c r="F52"/>
-      <c r="G52" t="n">
+      <c r="G52">
         <v>208984000000</v>
       </c>
       <c r="H52" t="s">
         <v>45</v>
       </c>
-      <c r="I52" t="n">
+      <c r="I52">
         <v>39646</v>
       </c>
       <c r="J52" t="s">
         <v>31</v>
       </c>
-      <c r="K52" t="n">
-        <v>1.854</v>
+      <c r="K52">
+        <v>1.8540000000000001</v>
       </c>
       <c r="L52" t="s">
         <v>51</v>
@@ -5204,36 +4869,30 @@
       <c r="N52" t="s">
         <v>34</v>
       </c>
-      <c r="O52"/>
-      <c r="P52"/>
-      <c r="Q52" t="n">
+      <c r="Q52">
         <v>18.7</v>
       </c>
-      <c r="R52"/>
-      <c r="S52"/>
       <c r="T52" t="b">
         <v>0</v>
       </c>
       <c r="U52" t="s">
         <v>248</v>
       </c>
-      <c r="V52"/>
-      <c r="W52"/>
       <c r="X52" t="s">
         <v>249</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Y52">
         <v>3</v>
       </c>
-      <c r="Z52" t="n">
+      <c r="Z52">
         <v>1</v>
       </c>
       <c r="AA52" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A53">
         <v>52</v>
       </c>
       <c r="B53" t="s">
@@ -5248,21 +4907,20 @@
       <c r="E53" t="s">
         <v>250</v>
       </c>
-      <c r="F53"/>
-      <c r="G53" t="n">
+      <c r="G53">
         <v>208984000000</v>
       </c>
       <c r="H53" t="s">
         <v>50</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I53">
         <v>39415</v>
       </c>
       <c r="J53" t="s">
         <v>31</v>
       </c>
-      <c r="K53" t="n">
-        <v>2.136</v>
+      <c r="K53">
+        <v>2.1360000000000001</v>
       </c>
       <c r="L53" t="s">
         <v>32</v>
@@ -5273,36 +4931,30 @@
       <c r="N53" t="s">
         <v>34</v>
       </c>
-      <c r="O53"/>
-      <c r="P53"/>
-      <c r="Q53" t="n">
+      <c r="Q53">
         <v>41.4</v>
       </c>
-      <c r="R53"/>
-      <c r="S53"/>
       <c r="T53" t="b">
         <v>0</v>
       </c>
       <c r="U53" t="s">
         <v>252</v>
       </c>
-      <c r="V53"/>
-      <c r="W53"/>
       <c r="X53" t="s">
         <v>253</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Y53">
         <v>4</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="Z53">
         <v>1</v>
       </c>
       <c r="AA53" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="n">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A54">
         <v>53</v>
       </c>
       <c r="B54" t="s">
@@ -5317,20 +4969,19 @@
       <c r="E54" t="s">
         <v>254</v>
       </c>
-      <c r="F54"/>
-      <c r="G54" t="n">
+      <c r="G54">
         <v>208984000000</v>
       </c>
       <c r="H54" t="s">
         <v>56</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I54">
         <v>39828</v>
       </c>
       <c r="J54" t="s">
         <v>31</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K54">
         <v>1.591</v>
       </c>
       <c r="L54" t="s">
@@ -5342,36 +4993,30 @@
       <c r="N54" t="s">
         <v>34</v>
       </c>
-      <c r="O54"/>
-      <c r="P54"/>
-      <c r="Q54" t="n">
+      <c r="Q54">
         <v>41.4</v>
       </c>
-      <c r="R54"/>
-      <c r="S54"/>
       <c r="T54" t="b">
         <v>0</v>
       </c>
       <c r="U54" t="s">
         <v>256</v>
       </c>
-      <c r="V54"/>
-      <c r="W54"/>
       <c r="X54" t="s">
         <v>257</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Y54">
         <v>5</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="Z54">
         <v>1</v>
       </c>
       <c r="AA54" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>54</v>
       </c>
       <c r="B55" t="s">
@@ -5386,20 +5031,19 @@
       <c r="E55" t="s">
         <v>258</v>
       </c>
-      <c r="F55"/>
-      <c r="G55" t="n">
+      <c r="G55">
         <v>208984000000</v>
       </c>
       <c r="H55" t="s">
         <v>61</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I55">
         <v>40111</v>
       </c>
       <c r="J55" t="s">
         <v>31</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K55">
         <v>0.312</v>
       </c>
       <c r="L55" t="s">
@@ -5411,36 +5055,30 @@
       <c r="N55" t="s">
         <v>34</v>
       </c>
-      <c r="O55"/>
-      <c r="P55"/>
-      <c r="Q55" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="R55"/>
-      <c r="S55"/>
+      <c r="Q55">
+        <v>18.600000000000001</v>
+      </c>
       <c r="T55" t="b">
         <v>0</v>
       </c>
       <c r="U55" t="s">
         <v>260</v>
       </c>
-      <c r="V55"/>
-      <c r="W55"/>
       <c r="X55" t="s">
         <v>261</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Y55">
         <v>6</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="Z55">
         <v>1</v>
       </c>
       <c r="AA55" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="n">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A56">
         <v>55</v>
       </c>
       <c r="B56" t="s">
@@ -5455,20 +5093,19 @@
       <c r="E56" t="s">
         <v>262</v>
       </c>
-      <c r="F56"/>
-      <c r="G56" t="n">
+      <c r="G56">
         <v>208984000000</v>
       </c>
       <c r="H56" t="s">
         <v>66</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I56">
         <v>40141</v>
       </c>
       <c r="J56" t="s">
         <v>31</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K56">
         <v>0.23</v>
       </c>
       <c r="L56" t="s">
@@ -5480,36 +5117,30 @@
       <c r="N56" t="s">
         <v>34</v>
       </c>
-      <c r="O56"/>
-      <c r="P56"/>
-      <c r="Q56" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="R56"/>
-      <c r="S56"/>
+      <c r="Q56">
+        <v>18.600000000000001</v>
+      </c>
       <c r="T56" t="b">
         <v>0</v>
       </c>
       <c r="U56" t="s">
         <v>264</v>
       </c>
-      <c r="V56"/>
-      <c r="W56"/>
       <c r="X56" t="s">
         <v>265</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Y56">
         <v>1</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="Z56">
         <v>2</v>
       </c>
       <c r="AA56" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="n">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A57">
         <v>56</v>
       </c>
       <c r="B57" t="s">
@@ -5524,20 +5155,19 @@
       <c r="E57" t="s">
         <v>266</v>
       </c>
-      <c r="F57"/>
-      <c r="G57" t="n">
+      <c r="G57">
         <v>208984000000</v>
       </c>
       <c r="H57" t="s">
         <v>71</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I57">
         <v>40108</v>
       </c>
       <c r="J57" t="s">
         <v>31</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K57">
         <v>0.312</v>
       </c>
       <c r="L57" t="s">
@@ -5549,36 +5179,30 @@
       <c r="N57" t="s">
         <v>34</v>
       </c>
-      <c r="O57"/>
-      <c r="P57"/>
-      <c r="Q57" t="n">
+      <c r="Q57">
         <v>21.5</v>
       </c>
-      <c r="R57"/>
-      <c r="S57"/>
       <c r="T57" t="b">
         <v>0</v>
       </c>
       <c r="U57" t="s">
         <v>268</v>
       </c>
-      <c r="V57"/>
-      <c r="W57"/>
       <c r="X57" t="s">
         <v>269</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Y57">
         <v>2</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="Z57">
         <v>2</v>
       </c>
       <c r="AA57" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="n">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A58">
         <v>57</v>
       </c>
       <c r="B58" t="s">
@@ -5593,21 +5217,20 @@
       <c r="E58" t="s">
         <v>270</v>
       </c>
-      <c r="F58"/>
-      <c r="G58" t="n">
+      <c r="G58">
         <v>208984000000</v>
       </c>
       <c r="H58" t="s">
         <v>76</v>
       </c>
-      <c r="I58" t="n">
+      <c r="I58">
         <v>40074</v>
       </c>
       <c r="J58" t="s">
         <v>31</v>
       </c>
-      <c r="K58" t="n">
-        <v>0.424</v>
+      <c r="K58">
+        <v>0.42399999999999999</v>
       </c>
       <c r="L58" t="s">
         <v>51</v>
@@ -5618,36 +5241,30 @@
       <c r="N58" t="s">
         <v>34</v>
       </c>
-      <c r="O58"/>
-      <c r="P58"/>
-      <c r="Q58" t="n">
+      <c r="Q58">
         <v>14.9</v>
       </c>
-      <c r="R58"/>
-      <c r="S58"/>
       <c r="T58" t="b">
         <v>0</v>
       </c>
       <c r="U58" t="s">
         <v>272</v>
       </c>
-      <c r="V58"/>
-      <c r="W58"/>
       <c r="X58" t="s">
         <v>273</v>
       </c>
-      <c r="Y58" t="n">
+      <c r="Y58">
         <v>3</v>
       </c>
-      <c r="Z58" t="n">
+      <c r="Z58">
         <v>2</v>
       </c>
       <c r="AA58" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" t="n">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A59">
         <v>58</v>
       </c>
       <c r="B59" t="s">
@@ -5662,21 +5279,20 @@
       <c r="E59" t="s">
         <v>274</v>
       </c>
-      <c r="F59"/>
-      <c r="G59" t="n">
+      <c r="G59">
         <v>208984000000</v>
       </c>
       <c r="H59" t="s">
         <v>81</v>
       </c>
-      <c r="I59" t="n">
+      <c r="I59">
         <v>39354</v>
       </c>
       <c r="J59" t="s">
         <v>31</v>
       </c>
-      <c r="K59" t="n">
-        <v>2.385</v>
+      <c r="K59">
+        <v>2.3849999999999998</v>
       </c>
       <c r="L59" t="s">
         <v>32</v>
@@ -5687,36 +5303,30 @@
       <c r="N59" t="s">
         <v>34</v>
       </c>
-      <c r="O59"/>
-      <c r="P59"/>
-      <c r="Q59" t="n">
+      <c r="Q59">
         <v>21.5</v>
       </c>
-      <c r="R59"/>
-      <c r="S59"/>
       <c r="T59" t="b">
         <v>0</v>
       </c>
       <c r="U59" t="s">
         <v>276</v>
       </c>
-      <c r="V59"/>
-      <c r="W59"/>
       <c r="X59" t="s">
         <v>277</v>
       </c>
-      <c r="Y59" t="n">
+      <c r="Y59">
         <v>4</v>
       </c>
-      <c r="Z59" t="n">
+      <c r="Z59">
         <v>2</v>
       </c>
       <c r="AA59" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="n">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A60">
         <v>59</v>
       </c>
       <c r="B60" t="s">
@@ -5731,21 +5341,20 @@
       <c r="E60" t="s">
         <v>278</v>
       </c>
-      <c r="F60"/>
-      <c r="G60" t="n">
+      <c r="G60">
         <v>208984000000</v>
       </c>
       <c r="H60" t="s">
         <v>86</v>
       </c>
-      <c r="I60" t="n">
+      <c r="I60">
         <v>40125</v>
       </c>
       <c r="J60" t="s">
         <v>31</v>
       </c>
-      <c r="K60" t="n">
-        <v>0.285</v>
+      <c r="K60">
+        <v>0.28499999999999998</v>
       </c>
       <c r="L60" t="s">
         <v>32</v>
@@ -5756,36 +5365,30 @@
       <c r="N60" t="s">
         <v>34</v>
       </c>
-      <c r="O60"/>
-      <c r="P60"/>
-      <c r="Q60" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R60"/>
-      <c r="S60"/>
+      <c r="Q60">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T60" t="b">
         <v>0</v>
       </c>
       <c r="U60" t="s">
         <v>280</v>
       </c>
-      <c r="V60"/>
-      <c r="W60"/>
       <c r="X60" t="s">
         <v>281</v>
       </c>
-      <c r="Y60" t="n">
+      <c r="Y60">
         <v>5</v>
       </c>
-      <c r="Z60" t="n">
+      <c r="Z60">
         <v>2</v>
       </c>
       <c r="AA60" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="n">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A61">
         <v>60</v>
       </c>
       <c r="B61" t="s">
@@ -5800,21 +5403,20 @@
       <c r="E61" t="s">
         <v>282</v>
       </c>
-      <c r="F61"/>
-      <c r="G61" t="n">
+      <c r="G61">
         <v>208984000000</v>
       </c>
       <c r="H61" t="s">
         <v>91</v>
       </c>
-      <c r="I61" t="n">
+      <c r="I61">
         <v>40054</v>
       </c>
       <c r="J61" t="s">
         <v>31</v>
       </c>
-      <c r="K61" t="n">
-        <v>0.572</v>
+      <c r="K61">
+        <v>0.57199999999999995</v>
       </c>
       <c r="L61" t="s">
         <v>51</v>
@@ -5825,36 +5427,30 @@
       <c r="N61" t="s">
         <v>34</v>
       </c>
-      <c r="O61"/>
-      <c r="P61"/>
-      <c r="Q61" t="n">
+      <c r="Q61">
         <v>14.9</v>
       </c>
-      <c r="R61"/>
-      <c r="S61"/>
       <c r="T61" t="b">
         <v>0</v>
       </c>
       <c r="U61" t="s">
         <v>284</v>
       </c>
-      <c r="V61"/>
-      <c r="W61"/>
       <c r="X61" t="s">
         <v>285</v>
       </c>
-      <c r="Y61" t="n">
+      <c r="Y61">
         <v>6</v>
       </c>
-      <c r="Z61" t="n">
+      <c r="Z61">
         <v>2</v>
       </c>
       <c r="AA61" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="n">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A62">
         <v>61</v>
       </c>
       <c r="B62" t="s">
@@ -5869,21 +5465,20 @@
       <c r="E62" t="s">
         <v>286</v>
       </c>
-      <c r="F62"/>
-      <c r="G62" t="n">
+      <c r="G62">
         <v>208984000000</v>
       </c>
       <c r="H62" t="s">
         <v>30</v>
       </c>
-      <c r="I62" t="n">
+      <c r="I62">
         <v>40067</v>
       </c>
       <c r="J62" t="s">
         <v>31</v>
       </c>
-      <c r="K62" t="n">
-        <v>0.474</v>
+      <c r="K62">
+        <v>0.47399999999999998</v>
       </c>
       <c r="L62" t="s">
         <v>51</v>
@@ -5894,36 +5489,30 @@
       <c r="N62" t="s">
         <v>34</v>
       </c>
-      <c r="O62"/>
-      <c r="P62"/>
-      <c r="Q62" t="n">
+      <c r="Q62">
         <v>19.3</v>
       </c>
-      <c r="R62"/>
-      <c r="S62"/>
       <c r="T62" t="b">
         <v>0</v>
       </c>
       <c r="U62" t="s">
         <v>288</v>
       </c>
-      <c r="V62"/>
-      <c r="W62"/>
       <c r="X62" t="s">
         <v>289</v>
       </c>
-      <c r="Y62" t="n">
+      <c r="Y62">
         <v>1</v>
       </c>
-      <c r="Z62" t="n">
+      <c r="Z62">
         <v>1</v>
       </c>
       <c r="AA62" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="n">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A63">
         <v>62</v>
       </c>
       <c r="B63" t="s">
@@ -5938,21 +5527,20 @@
       <c r="E63" t="s">
         <v>290</v>
       </c>
-      <c r="F63"/>
-      <c r="G63" t="n">
+      <c r="G63">
         <v>208984000000</v>
       </c>
       <c r="H63" t="s">
         <v>40</v>
       </c>
-      <c r="I63" t="n">
+      <c r="I63">
         <v>39788</v>
       </c>
       <c r="J63" t="s">
         <v>31</v>
       </c>
-      <c r="K63" t="n">
-        <v>1.662</v>
+      <c r="K63">
+        <v>1.6619999999999999</v>
       </c>
       <c r="L63" t="s">
         <v>32</v>
@@ -5963,36 +5551,30 @@
       <c r="N63" t="s">
         <v>34</v>
       </c>
-      <c r="O63"/>
-      <c r="P63"/>
-      <c r="Q63" t="n">
+      <c r="Q63">
         <v>25</v>
       </c>
-      <c r="R63"/>
-      <c r="S63"/>
       <c r="T63" t="b">
         <v>0</v>
       </c>
       <c r="U63" t="s">
         <v>292</v>
       </c>
-      <c r="V63"/>
-      <c r="W63"/>
       <c r="X63" t="s">
         <v>293</v>
       </c>
-      <c r="Y63" t="n">
+      <c r="Y63">
         <v>2</v>
       </c>
-      <c r="Z63" t="n">
+      <c r="Z63">
         <v>1</v>
       </c>
       <c r="AA63" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="n">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A64">
         <v>63</v>
       </c>
       <c r="B64" t="s">
@@ -6007,21 +5589,20 @@
       <c r="E64" t="s">
         <v>294</v>
       </c>
-      <c r="F64"/>
-      <c r="G64" t="n">
+      <c r="G64">
         <v>208984000000</v>
       </c>
       <c r="H64" t="s">
         <v>45</v>
       </c>
-      <c r="I64" t="n">
+      <c r="I64">
         <v>39643</v>
       </c>
       <c r="J64" t="s">
         <v>31</v>
       </c>
-      <c r="K64" t="n">
-        <v>1.862</v>
+      <c r="K64">
+        <v>1.8620000000000001</v>
       </c>
       <c r="L64" t="s">
         <v>51</v>
@@ -6032,36 +5613,30 @@
       <c r="N64" t="s">
         <v>34</v>
       </c>
-      <c r="O64"/>
-      <c r="P64"/>
-      <c r="Q64" t="n">
+      <c r="Q64">
         <v>20</v>
       </c>
-      <c r="R64"/>
-      <c r="S64"/>
       <c r="T64" t="b">
         <v>0</v>
       </c>
       <c r="U64" t="s">
         <v>296</v>
       </c>
-      <c r="V64"/>
-      <c r="W64"/>
       <c r="X64" t="s">
         <v>297</v>
       </c>
-      <c r="Y64" t="n">
+      <c r="Y64">
         <v>3</v>
       </c>
-      <c r="Z64" t="n">
+      <c r="Z64">
         <v>1</v>
       </c>
       <c r="AA64" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" t="n">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A65">
         <v>64</v>
       </c>
       <c r="B65" t="s">
@@ -6076,21 +5651,20 @@
       <c r="E65" t="s">
         <v>298</v>
       </c>
-      <c r="F65"/>
-      <c r="G65" t="n">
+      <c r="G65">
         <v>208984000000</v>
       </c>
       <c r="H65" t="s">
         <v>50</v>
       </c>
-      <c r="I65" t="n">
+      <c r="I65">
         <v>39895</v>
       </c>
       <c r="J65" t="s">
         <v>31</v>
       </c>
-      <c r="K65" t="n">
-        <v>1.481</v>
+      <c r="K65">
+        <v>1.4810000000000001</v>
       </c>
       <c r="L65" t="s">
         <v>32</v>
@@ -6101,36 +5675,30 @@
       <c r="N65" t="s">
         <v>34</v>
       </c>
-      <c r="O65"/>
-      <c r="P65"/>
-      <c r="Q65" t="n">
+      <c r="Q65">
         <v>18.7</v>
       </c>
-      <c r="R65"/>
-      <c r="S65"/>
       <c r="T65" t="b">
         <v>0</v>
       </c>
       <c r="U65" t="s">
         <v>300</v>
       </c>
-      <c r="V65"/>
-      <c r="W65"/>
       <c r="X65" t="s">
         <v>301</v>
       </c>
-      <c r="Y65" t="n">
+      <c r="Y65">
         <v>4</v>
       </c>
-      <c r="Z65" t="n">
+      <c r="Z65">
         <v>1</v>
       </c>
       <c r="AA65" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="n">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A66">
         <v>65</v>
       </c>
       <c r="B66" t="s">
@@ -6145,21 +5713,20 @@
       <c r="E66" t="s">
         <v>302</v>
       </c>
-      <c r="F66"/>
-      <c r="G66" t="n">
+      <c r="G66">
         <v>208984000000</v>
       </c>
       <c r="H66" t="s">
         <v>56</v>
       </c>
-      <c r="I66" t="n">
+      <c r="I66">
         <v>40102</v>
       </c>
       <c r="J66" t="s">
         <v>31</v>
       </c>
-      <c r="K66" t="n">
-        <v>0.329</v>
+      <c r="K66">
+        <v>0.32900000000000001</v>
       </c>
       <c r="L66" t="s">
         <v>32</v>
@@ -6170,36 +5737,30 @@
       <c r="N66" t="s">
         <v>34</v>
       </c>
-      <c r="O66"/>
-      <c r="P66"/>
-      <c r="Q66" t="n">
+      <c r="Q66">
         <v>20.8</v>
       </c>
-      <c r="R66"/>
-      <c r="S66"/>
       <c r="T66" t="b">
         <v>0</v>
       </c>
       <c r="U66" t="s">
         <v>304</v>
       </c>
-      <c r="V66"/>
-      <c r="W66"/>
       <c r="X66" t="s">
         <v>305</v>
       </c>
-      <c r="Y66" t="n">
+      <c r="Y66">
         <v>5</v>
       </c>
-      <c r="Z66" t="n">
+      <c r="Z66">
         <v>1</v>
       </c>
       <c r="AA66" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="n">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A67">
         <v>66</v>
       </c>
       <c r="B67" t="s">
@@ -6214,21 +5775,20 @@
       <c r="E67" t="s">
         <v>306</v>
       </c>
-      <c r="F67"/>
-      <c r="G67" t="n">
+      <c r="G67">
         <v>208984000000</v>
       </c>
       <c r="H67" t="s">
         <v>61</v>
       </c>
-      <c r="I67" t="n">
+      <c r="I67">
         <v>39903</v>
       </c>
       <c r="J67" t="s">
         <v>31</v>
       </c>
-      <c r="K67" t="n">
-        <v>1.516769336</v>
+      <c r="K67">
+        <v>1.5167693360000001</v>
       </c>
       <c r="L67" t="s">
         <v>32</v>
@@ -6239,36 +5799,30 @@
       <c r="N67" t="s">
         <v>34</v>
       </c>
-      <c r="O67"/>
-      <c r="P67"/>
-      <c r="Q67" t="n">
+      <c r="Q67">
         <v>31.8</v>
       </c>
-      <c r="R67"/>
-      <c r="S67"/>
       <c r="T67" t="b">
         <v>0</v>
       </c>
       <c r="U67" t="s">
         <v>308</v>
       </c>
-      <c r="V67"/>
-      <c r="W67"/>
       <c r="X67" t="s">
         <v>309</v>
       </c>
-      <c r="Y67" t="n">
+      <c r="Y67">
         <v>6</v>
       </c>
-      <c r="Z67" t="n">
+      <c r="Z67">
         <v>1</v>
       </c>
       <c r="AA67" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="n">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A68">
         <v>67</v>
       </c>
       <c r="B68" t="s">
@@ -6283,21 +5837,20 @@
       <c r="E68" t="s">
         <v>310</v>
       </c>
-      <c r="F68"/>
-      <c r="G68" t="n">
+      <c r="G68">
         <v>208984000000</v>
       </c>
       <c r="H68" t="s">
         <v>66</v>
       </c>
-      <c r="I68" t="n">
+      <c r="I68">
         <v>39701</v>
       </c>
       <c r="J68" t="s">
         <v>31</v>
       </c>
-      <c r="K68" t="n">
-        <v>1.815</v>
+      <c r="K68">
+        <v>1.8149999999999999</v>
       </c>
       <c r="L68" t="s">
         <v>51</v>
@@ -6308,36 +5861,30 @@
       <c r="N68" t="s">
         <v>34</v>
       </c>
-      <c r="O68"/>
-      <c r="P68"/>
-      <c r="Q68" t="n">
+      <c r="Q68">
         <v>34.4</v>
       </c>
-      <c r="R68"/>
-      <c r="S68"/>
       <c r="T68" t="b">
         <v>0</v>
       </c>
       <c r="U68" t="s">
         <v>312</v>
       </c>
-      <c r="V68"/>
-      <c r="W68"/>
       <c r="X68" t="s">
         <v>313</v>
       </c>
-      <c r="Y68" t="n">
+      <c r="Y68">
         <v>1</v>
       </c>
-      <c r="Z68" t="n">
+      <c r="Z68">
         <v>2</v>
       </c>
       <c r="AA68" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="n">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A69">
         <v>68</v>
       </c>
       <c r="B69" t="s">
@@ -6352,21 +5899,20 @@
       <c r="E69" t="s">
         <v>314</v>
       </c>
-      <c r="F69"/>
-      <c r="G69" t="n">
+      <c r="G69">
         <v>208984000000</v>
       </c>
       <c r="H69" t="s">
         <v>71</v>
       </c>
-      <c r="I69" t="n">
+      <c r="I69">
         <v>39892</v>
       </c>
       <c r="J69" t="s">
         <v>31</v>
       </c>
-      <c r="K69" t="n">
-        <v>1.481</v>
+      <c r="K69">
+        <v>1.4810000000000001</v>
       </c>
       <c r="L69" t="s">
         <v>51</v>
@@ -6377,36 +5923,30 @@
       <c r="N69" t="s">
         <v>34</v>
       </c>
-      <c r="O69"/>
-      <c r="P69"/>
-      <c r="Q69" t="n">
+      <c r="Q69">
         <v>18.7</v>
       </c>
-      <c r="R69"/>
-      <c r="S69"/>
       <c r="T69" t="b">
         <v>0</v>
       </c>
       <c r="U69" t="s">
         <v>316</v>
       </c>
-      <c r="V69"/>
-      <c r="W69"/>
       <c r="X69" t="s">
         <v>317</v>
       </c>
-      <c r="Y69" t="n">
+      <c r="Y69">
         <v>2</v>
       </c>
-      <c r="Z69" t="n">
+      <c r="Z69">
         <v>2</v>
       </c>
       <c r="AA69" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="n">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A70">
         <v>69</v>
       </c>
       <c r="B70" t="s">
@@ -6421,21 +5961,20 @@
       <c r="E70" t="s">
         <v>318</v>
       </c>
-      <c r="F70"/>
-      <c r="G70" t="n">
+      <c r="G70">
         <v>208984000000</v>
       </c>
       <c r="H70" t="s">
         <v>76</v>
       </c>
-      <c r="I70" t="n">
+      <c r="I70">
         <v>39770</v>
       </c>
       <c r="J70" t="s">
         <v>31</v>
       </c>
-      <c r="K70" t="n">
-        <v>1.703</v>
+      <c r="K70">
+        <v>1.7030000000000001</v>
       </c>
       <c r="L70" t="s">
         <v>32</v>
@@ -6446,36 +5985,30 @@
       <c r="N70" t="s">
         <v>34</v>
       </c>
-      <c r="O70"/>
-      <c r="P70"/>
-      <c r="Q70" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R70"/>
-      <c r="S70"/>
+      <c r="Q70">
+        <v>19.600000000000001</v>
+      </c>
       <c r="T70" t="b">
         <v>0</v>
       </c>
       <c r="U70" t="s">
         <v>320</v>
       </c>
-      <c r="V70"/>
-      <c r="W70"/>
       <c r="X70" t="s">
         <v>321</v>
       </c>
-      <c r="Y70" t="n">
+      <c r="Y70">
         <v>3</v>
       </c>
-      <c r="Z70" t="n">
+      <c r="Z70">
         <v>2</v>
       </c>
       <c r="AA70" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="n">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A71">
         <v>70</v>
       </c>
       <c r="B71" t="s">
@@ -6490,20 +6023,19 @@
       <c r="E71" t="s">
         <v>322</v>
       </c>
-      <c r="F71"/>
-      <c r="G71" t="n">
+      <c r="G71">
         <v>208984000000</v>
       </c>
       <c r="H71" t="s">
         <v>81</v>
       </c>
-      <c r="I71" t="n">
+      <c r="I71">
         <v>40113</v>
       </c>
       <c r="J71" t="s">
         <v>31</v>
       </c>
-      <c r="K71" t="n">
+      <c r="K71">
         <v>0.312</v>
       </c>
       <c r="L71" t="s">
@@ -6515,36 +6047,30 @@
       <c r="N71" t="s">
         <v>34</v>
       </c>
-      <c r="O71"/>
-      <c r="P71"/>
-      <c r="Q71" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="R71"/>
-      <c r="S71"/>
+      <c r="Q71">
+        <v>18.600000000000001</v>
+      </c>
       <c r="T71" t="b">
         <v>0</v>
       </c>
       <c r="U71" t="s">
         <v>324</v>
       </c>
-      <c r="V71"/>
-      <c r="W71"/>
       <c r="X71" t="s">
         <v>325</v>
       </c>
-      <c r="Y71" t="n">
+      <c r="Y71">
         <v>4</v>
       </c>
-      <c r="Z71" t="n">
+      <c r="Z71">
         <v>2</v>
       </c>
       <c r="AA71" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="n">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A72">
         <v>71</v>
       </c>
       <c r="B72" t="s">
@@ -6559,20 +6085,19 @@
       <c r="E72" t="s">
         <v>326</v>
       </c>
-      <c r="F72"/>
-      <c r="G72" t="n">
+      <c r="G72">
         <v>208984000000</v>
       </c>
       <c r="H72" t="s">
         <v>86</v>
       </c>
-      <c r="I72" t="n">
+      <c r="I72">
         <v>39725</v>
       </c>
       <c r="J72" t="s">
         <v>31</v>
       </c>
-      <c r="K72" t="n">
+      <c r="K72">
         <v>1.744</v>
       </c>
       <c r="L72" t="s">
@@ -6584,36 +6109,30 @@
       <c r="N72" t="s">
         <v>34</v>
       </c>
-      <c r="O72"/>
-      <c r="P72"/>
-      <c r="Q72" t="n">
+      <c r="Q72">
         <v>13.9</v>
       </c>
-      <c r="R72"/>
-      <c r="S72"/>
       <c r="T72" t="b">
         <v>0</v>
       </c>
       <c r="U72" t="s">
         <v>328</v>
       </c>
-      <c r="V72"/>
-      <c r="W72"/>
       <c r="X72" t="s">
         <v>329</v>
       </c>
-      <c r="Y72" t="n">
+      <c r="Y72">
         <v>5</v>
       </c>
-      <c r="Z72" t="n">
+      <c r="Z72">
         <v>2</v>
       </c>
       <c r="AA72" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="n">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A73">
         <v>72</v>
       </c>
       <c r="B73" t="s">
@@ -6628,21 +6147,20 @@
       <c r="E73" t="s">
         <v>330</v>
       </c>
-      <c r="F73"/>
-      <c r="G73" t="n">
+      <c r="G73">
         <v>208984000000</v>
       </c>
       <c r="H73" t="s">
         <v>91</v>
       </c>
-      <c r="I73" t="n">
+      <c r="I73">
         <v>39829</v>
       </c>
       <c r="J73" t="s">
         <v>31</v>
       </c>
-      <c r="K73" t="n">
-        <v>1.648186174</v>
+      <c r="K73">
+        <v>1.6481861739999999</v>
       </c>
       <c r="L73" t="s">
         <v>51</v>
@@ -6653,36 +6171,30 @@
       <c r="N73" t="s">
         <v>34</v>
       </c>
-      <c r="O73"/>
-      <c r="P73"/>
-      <c r="Q73" t="n">
+      <c r="Q73">
         <v>41.4</v>
       </c>
-      <c r="R73"/>
-      <c r="S73"/>
       <c r="T73" t="b">
         <v>0</v>
       </c>
       <c r="U73" t="s">
         <v>332</v>
       </c>
-      <c r="V73"/>
-      <c r="W73"/>
       <c r="X73" t="s">
         <v>333</v>
       </c>
-      <c r="Y73" t="n">
+      <c r="Y73">
         <v>6</v>
       </c>
-      <c r="Z73" t="n">
+      <c r="Z73">
         <v>2</v>
       </c>
       <c r="AA73" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="n">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A74">
         <v>73</v>
       </c>
       <c r="B74" t="s">
@@ -6697,21 +6209,20 @@
       <c r="E74" t="s">
         <v>334</v>
       </c>
-      <c r="F74"/>
-      <c r="G74" t="n">
+      <c r="G74">
         <v>208984000000</v>
       </c>
       <c r="H74" t="s">
         <v>30</v>
       </c>
-      <c r="I74" t="n">
+      <c r="I74">
         <v>40056</v>
       </c>
       <c r="J74" t="s">
         <v>31</v>
       </c>
-      <c r="K74" t="n">
-        <v>0.539</v>
+      <c r="K74">
+        <v>0.53900000000000003</v>
       </c>
       <c r="L74" t="s">
         <v>51</v>
@@ -6722,36 +6233,30 @@
       <c r="N74" t="s">
         <v>34</v>
       </c>
-      <c r="O74"/>
-      <c r="P74"/>
-      <c r="Q74" t="n">
+      <c r="Q74">
         <v>19.3</v>
       </c>
-      <c r="R74"/>
-      <c r="S74"/>
       <c r="T74" t="b">
         <v>0</v>
       </c>
       <c r="U74" t="s">
         <v>336</v>
       </c>
-      <c r="V74"/>
-      <c r="W74"/>
       <c r="X74" t="s">
         <v>337</v>
       </c>
-      <c r="Y74" t="n">
+      <c r="Y74">
         <v>1</v>
       </c>
-      <c r="Z74" t="n">
+      <c r="Z74">
         <v>1</v>
       </c>
       <c r="AA74" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="n">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A75">
         <v>74</v>
       </c>
       <c r="B75" t="s">
@@ -6766,20 +6271,19 @@
       <c r="E75" t="s">
         <v>338</v>
       </c>
-      <c r="F75"/>
-      <c r="G75" t="n">
+      <c r="G75">
         <v>208984000000</v>
       </c>
       <c r="H75" t="s">
         <v>40</v>
       </c>
-      <c r="I75" t="n">
+      <c r="I75">
         <v>40106</v>
       </c>
       <c r="J75" t="s">
         <v>31</v>
       </c>
-      <c r="K75" t="n">
+      <c r="K75">
         <v>0.312</v>
       </c>
       <c r="L75" t="s">
@@ -6791,36 +6295,30 @@
       <c r="N75" t="s">
         <v>34</v>
       </c>
-      <c r="O75"/>
-      <c r="P75"/>
-      <c r="Q75" t="n">
+      <c r="Q75">
         <v>21.5</v>
       </c>
-      <c r="R75"/>
-      <c r="S75"/>
       <c r="T75" t="b">
         <v>0</v>
       </c>
       <c r="U75" t="s">
         <v>340</v>
       </c>
-      <c r="V75"/>
-      <c r="W75"/>
       <c r="X75" t="s">
         <v>341</v>
       </c>
-      <c r="Y75" t="n">
+      <c r="Y75">
         <v>2</v>
       </c>
-      <c r="Z75" t="n">
+      <c r="Z75">
         <v>1</v>
       </c>
       <c r="AA75" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="n">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A76">
         <v>75</v>
       </c>
       <c r="B76" t="s">
@@ -6835,21 +6333,20 @@
       <c r="E76" t="s">
         <v>342</v>
       </c>
-      <c r="F76"/>
-      <c r="G76" t="n">
+      <c r="G76">
         <v>208984000000</v>
       </c>
       <c r="H76" t="s">
         <v>45</v>
       </c>
-      <c r="I76" t="n">
+      <c r="I76">
         <v>40138</v>
       </c>
       <c r="J76" t="s">
         <v>31</v>
       </c>
-      <c r="K76" t="n">
-        <v>0.233</v>
+      <c r="K76">
+        <v>0.23300000000000001</v>
       </c>
       <c r="L76" t="s">
         <v>51</v>
@@ -6860,36 +6357,30 @@
       <c r="N76" t="s">
         <v>34</v>
       </c>
-      <c r="O76"/>
-      <c r="P76"/>
-      <c r="Q76" t="n">
+      <c r="Q76">
         <v>21.5</v>
       </c>
-      <c r="R76"/>
-      <c r="S76"/>
       <c r="T76" t="b">
         <v>0</v>
       </c>
       <c r="U76" t="s">
         <v>344</v>
       </c>
-      <c r="V76"/>
-      <c r="W76"/>
       <c r="X76" t="s">
         <v>345</v>
       </c>
-      <c r="Y76" t="n">
+      <c r="Y76">
         <v>3</v>
       </c>
-      <c r="Z76" t="n">
+      <c r="Z76">
         <v>1</v>
       </c>
       <c r="AA76" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="n">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A77">
         <v>76</v>
       </c>
       <c r="B77" t="s">
@@ -6904,21 +6395,20 @@
       <c r="E77" t="s">
         <v>346</v>
       </c>
-      <c r="F77"/>
-      <c r="G77" t="n">
+      <c r="G77">
         <v>208984000000</v>
       </c>
       <c r="H77" t="s">
         <v>50</v>
       </c>
-      <c r="I77" t="n">
+      <c r="I77">
         <v>39769</v>
       </c>
       <c r="J77" t="s">
         <v>31</v>
       </c>
-      <c r="K77" t="n">
-        <v>1.703</v>
+      <c r="K77">
+        <v>1.7030000000000001</v>
       </c>
       <c r="L77" t="s">
         <v>32</v>
@@ -6929,36 +6419,30 @@
       <c r="N77" t="s">
         <v>34</v>
       </c>
-      <c r="O77"/>
-      <c r="P77"/>
-      <c r="Q77" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="R77"/>
-      <c r="S77"/>
+      <c r="Q77">
+        <v>19.600000000000001</v>
+      </c>
       <c r="T77" t="b">
         <v>0</v>
       </c>
       <c r="U77" t="s">
         <v>348</v>
       </c>
-      <c r="V77"/>
-      <c r="W77"/>
       <c r="X77" t="s">
         <v>349</v>
       </c>
-      <c r="Y77" t="n">
+      <c r="Y77">
         <v>4</v>
       </c>
-      <c r="Z77" t="n">
+      <c r="Z77">
         <v>1</v>
       </c>
       <c r="AA77" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="n">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A78">
         <v>77</v>
       </c>
       <c r="B78" t="s">
@@ -6973,21 +6457,20 @@
       <c r="E78" t="s">
         <v>350</v>
       </c>
-      <c r="F78"/>
-      <c r="G78" t="n">
+      <c r="G78">
         <v>208984000000</v>
       </c>
       <c r="H78" t="s">
         <v>56</v>
       </c>
-      <c r="I78" t="n">
+      <c r="I78">
         <v>39444</v>
       </c>
       <c r="J78" t="s">
         <v>31</v>
       </c>
-      <c r="K78" t="n">
-        <v>2.256</v>
+      <c r="K78">
+        <v>2.2559999999999998</v>
       </c>
       <c r="L78" t="s">
         <v>51</v>
@@ -6998,36 +6481,30 @@
       <c r="N78" t="s">
         <v>34</v>
       </c>
-      <c r="O78"/>
-      <c r="P78"/>
-      <c r="Q78" t="n">
+      <c r="Q78">
         <v>21.7</v>
       </c>
-      <c r="R78"/>
-      <c r="S78"/>
       <c r="T78" t="b">
         <v>0</v>
       </c>
       <c r="U78" t="s">
         <v>352</v>
       </c>
-      <c r="V78"/>
-      <c r="W78"/>
       <c r="X78" t="s">
         <v>353</v>
       </c>
-      <c r="Y78" t="n">
+      <c r="Y78">
         <v>5</v>
       </c>
-      <c r="Z78" t="n">
+      <c r="Z78">
         <v>1</v>
       </c>
       <c r="AA78" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="n">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A79">
         <v>78</v>
       </c>
       <c r="B79" t="s">
@@ -7042,20 +6519,19 @@
       <c r="E79" t="s">
         <v>354</v>
       </c>
-      <c r="F79"/>
-      <c r="G79" t="n">
+      <c r="G79">
         <v>208984000000</v>
       </c>
       <c r="H79" t="s">
         <v>61</v>
       </c>
-      <c r="I79" t="n">
+      <c r="I79">
         <v>40107</v>
       </c>
       <c r="J79" t="s">
         <v>31</v>
       </c>
-      <c r="K79" t="n">
+      <c r="K79">
         <v>0.312</v>
       </c>
       <c r="L79" t="s">
@@ -7067,36 +6543,30 @@
       <c r="N79" t="s">
         <v>34</v>
       </c>
-      <c r="O79"/>
-      <c r="P79"/>
-      <c r="Q79" t="n">
+      <c r="Q79">
         <v>21.5</v>
       </c>
-      <c r="R79"/>
-      <c r="S79"/>
       <c r="T79" t="b">
         <v>0</v>
       </c>
       <c r="U79" t="s">
         <v>356</v>
       </c>
-      <c r="V79"/>
-      <c r="W79"/>
       <c r="X79" t="s">
         <v>357</v>
       </c>
-      <c r="Y79" t="n">
+      <c r="Y79">
         <v>6</v>
       </c>
-      <c r="Z79" t="n">
+      <c r="Z79">
         <v>1</v>
       </c>
       <c r="AA79" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="n">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A80">
         <v>79</v>
       </c>
       <c r="B80" t="s">
@@ -7111,20 +6581,19 @@
       <c r="E80" t="s">
         <v>358</v>
       </c>
-      <c r="F80"/>
-      <c r="G80" t="n">
+      <c r="G80">
         <v>208984000000</v>
       </c>
       <c r="H80" t="s">
         <v>66</v>
       </c>
-      <c r="I80" t="n">
+      <c r="I80">
         <v>39755</v>
       </c>
       <c r="J80" t="s">
         <v>31</v>
       </c>
-      <c r="K80" t="n">
+      <c r="K80">
         <v>1.73</v>
       </c>
       <c r="L80" t="s">
@@ -7136,36 +6605,30 @@
       <c r="N80" t="s">
         <v>34</v>
       </c>
-      <c r="O80"/>
-      <c r="P80"/>
-      <c r="Q80" t="n">
+      <c r="Q80">
         <v>15.9</v>
       </c>
-      <c r="R80"/>
-      <c r="S80"/>
       <c r="T80" t="b">
         <v>0</v>
       </c>
       <c r="U80" t="s">
         <v>360</v>
       </c>
-      <c r="V80"/>
-      <c r="W80"/>
       <c r="X80" t="s">
         <v>361</v>
       </c>
-      <c r="Y80" t="n">
+      <c r="Y80">
         <v>1</v>
       </c>
-      <c r="Z80" t="n">
+      <c r="Z80">
         <v>2</v>
       </c>
       <c r="AA80" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" t="n">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A81">
         <v>80</v>
       </c>
       <c r="B81" t="s">
@@ -7180,21 +6643,20 @@
       <c r="E81" t="s">
         <v>362</v>
       </c>
-      <c r="F81"/>
-      <c r="G81" t="n">
+      <c r="G81">
         <v>208984000000</v>
       </c>
       <c r="H81" t="s">
         <v>71</v>
       </c>
-      <c r="I81" t="n">
+      <c r="I81">
         <v>40098</v>
       </c>
       <c r="J81" t="s">
         <v>31</v>
       </c>
-      <c r="K81" t="n">
-        <v>0.356</v>
+      <c r="K81">
+        <v>0.35599999999999998</v>
       </c>
       <c r="L81" t="s">
         <v>32</v>
@@ -7205,36 +6667,30 @@
       <c r="N81" t="s">
         <v>34</v>
       </c>
-      <c r="O81"/>
-      <c r="P81"/>
-      <c r="Q81" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R81"/>
-      <c r="S81"/>
+      <c r="Q81">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T81" t="b">
         <v>0</v>
       </c>
       <c r="U81" t="s">
         <v>364</v>
       </c>
-      <c r="V81"/>
-      <c r="W81"/>
       <c r="X81" t="s">
         <v>365</v>
       </c>
-      <c r="Y81" t="n">
+      <c r="Y81">
         <v>2</v>
       </c>
-      <c r="Z81" t="n">
+      <c r="Z81">
         <v>2</v>
       </c>
       <c r="AA81" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="n">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A82">
         <v>81</v>
       </c>
       <c r="B82" t="s">
@@ -7249,21 +6705,20 @@
       <c r="E82" t="s">
         <v>366</v>
       </c>
-      <c r="F82"/>
-      <c r="G82" t="n">
+      <c r="G82">
         <v>208984000000</v>
       </c>
       <c r="H82" t="s">
         <v>76</v>
       </c>
-      <c r="I82" t="n">
+      <c r="I82">
         <v>40084</v>
       </c>
       <c r="J82" t="s">
         <v>31</v>
       </c>
-      <c r="K82" t="n">
-        <v>0.381</v>
+      <c r="K82">
+        <v>0.38100000000000001</v>
       </c>
       <c r="L82" t="s">
         <v>51</v>
@@ -7274,36 +6729,30 @@
       <c r="N82" t="s">
         <v>34</v>
       </c>
-      <c r="O82"/>
-      <c r="P82"/>
-      <c r="Q82" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="R82"/>
-      <c r="S82"/>
+      <c r="Q82">
+        <v>18.600000000000001</v>
+      </c>
       <c r="T82" t="b">
         <v>0</v>
       </c>
       <c r="U82" t="s">
         <v>368</v>
       </c>
-      <c r="V82"/>
-      <c r="W82"/>
       <c r="X82" t="s">
         <v>369</v>
       </c>
-      <c r="Y82" t="n">
+      <c r="Y82">
         <v>3</v>
       </c>
-      <c r="Z82" t="n">
+      <c r="Z82">
         <v>2</v>
       </c>
       <c r="AA82" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="n">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A83">
         <v>82</v>
       </c>
       <c r="B83" t="s">
@@ -7318,20 +6767,19 @@
       <c r="E83" t="s">
         <v>370</v>
       </c>
-      <c r="F83"/>
-      <c r="G83" t="n">
+      <c r="G83">
         <v>208984000000</v>
       </c>
       <c r="H83" t="s">
         <v>81</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I83">
         <v>40089</v>
       </c>
       <c r="J83" t="s">
         <v>31</v>
       </c>
-      <c r="K83" t="n">
+      <c r="K83">
         <v>0.372</v>
       </c>
       <c r="L83" t="s">
@@ -7343,36 +6791,30 @@
       <c r="N83" t="s">
         <v>34</v>
       </c>
-      <c r="O83"/>
-      <c r="P83"/>
-      <c r="Q83" t="n">
+      <c r="Q83">
         <v>26.4</v>
       </c>
-      <c r="R83"/>
-      <c r="S83"/>
       <c r="T83" t="b">
         <v>0</v>
       </c>
       <c r="U83" t="s">
         <v>372</v>
       </c>
-      <c r="V83"/>
-      <c r="W83"/>
       <c r="X83" t="s">
         <v>373</v>
       </c>
-      <c r="Y83" t="n">
+      <c r="Y83">
         <v>4</v>
       </c>
-      <c r="Z83" t="n">
+      <c r="Z83">
         <v>2</v>
       </c>
       <c r="AA83" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" t="n">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A84">
         <v>83</v>
       </c>
       <c r="B84" t="s">
@@ -7387,21 +6829,20 @@
       <c r="E84" t="s">
         <v>374</v>
       </c>
-      <c r="F84"/>
-      <c r="G84" t="n">
+      <c r="G84">
         <v>208984000000</v>
       </c>
       <c r="H84" t="s">
         <v>86</v>
       </c>
-      <c r="I84" t="n">
+      <c r="I84">
         <v>40127</v>
       </c>
       <c r="J84" t="s">
         <v>31</v>
       </c>
-      <c r="K84" t="n">
-        <v>0.285</v>
+      <c r="K84">
+        <v>0.28499999999999998</v>
       </c>
       <c r="L84" t="s">
         <v>32</v>
@@ -7412,36 +6853,30 @@
       <c r="N84" t="s">
         <v>34</v>
       </c>
-      <c r="O84"/>
-      <c r="P84"/>
-      <c r="Q84" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R84"/>
-      <c r="S84"/>
+      <c r="Q84">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T84" t="b">
         <v>0</v>
       </c>
       <c r="U84" t="s">
         <v>376</v>
       </c>
-      <c r="V84"/>
-      <c r="W84"/>
       <c r="X84" t="s">
         <v>377</v>
       </c>
-      <c r="Y84" t="n">
+      <c r="Y84">
         <v>5</v>
       </c>
-      <c r="Z84" t="n">
+      <c r="Z84">
         <v>2</v>
       </c>
       <c r="AA84" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="n">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A85">
         <v>84</v>
       </c>
       <c r="B85" t="s">
@@ -7456,21 +6891,20 @@
       <c r="E85" t="s">
         <v>378</v>
       </c>
-      <c r="F85"/>
-      <c r="G85" t="n">
+      <c r="G85">
         <v>208984000000</v>
       </c>
       <c r="H85" t="s">
         <v>91</v>
       </c>
-      <c r="I85" t="n">
+      <c r="I85">
         <v>40081</v>
       </c>
       <c r="J85" t="s">
         <v>31</v>
       </c>
-      <c r="K85" t="n">
-        <v>0.386</v>
+      <c r="K85">
+        <v>0.38600000000000001</v>
       </c>
       <c r="L85" t="s">
         <v>32</v>
@@ -7481,36 +6915,30 @@
       <c r="N85" t="s">
         <v>34</v>
       </c>
-      <c r="O85"/>
-      <c r="P85"/>
-      <c r="Q85" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R85"/>
-      <c r="S85"/>
+      <c r="Q85">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T85" t="b">
         <v>0</v>
       </c>
       <c r="U85" t="s">
         <v>380</v>
       </c>
-      <c r="V85"/>
-      <c r="W85"/>
       <c r="X85" t="s">
         <v>381</v>
       </c>
-      <c r="Y85" t="n">
+      <c r="Y85">
         <v>6</v>
       </c>
-      <c r="Z85" t="n">
+      <c r="Z85">
         <v>2</v>
       </c>
       <c r="AA85" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="n">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A86">
         <v>85</v>
       </c>
       <c r="B86" t="s">
@@ -7525,20 +6953,19 @@
       <c r="E86" t="s">
         <v>382</v>
       </c>
-      <c r="F86"/>
-      <c r="G86" t="n">
+      <c r="G86">
         <v>208984000000</v>
       </c>
       <c r="H86" t="s">
         <v>30</v>
       </c>
-      <c r="I86" t="n">
+      <c r="I86">
         <v>40092</v>
       </c>
       <c r="J86" t="s">
         <v>31</v>
       </c>
-      <c r="K86" t="n">
+      <c r="K86">
         <v>0.372</v>
       </c>
       <c r="L86" t="s">
@@ -7550,36 +6977,30 @@
       <c r="N86" t="s">
         <v>34</v>
       </c>
-      <c r="O86"/>
-      <c r="P86"/>
-      <c r="Q86" t="n">
+      <c r="Q86">
         <v>26.4</v>
       </c>
-      <c r="R86"/>
-      <c r="S86"/>
       <c r="T86" t="b">
         <v>0</v>
       </c>
       <c r="U86" t="s">
         <v>384</v>
       </c>
-      <c r="V86"/>
-      <c r="W86"/>
       <c r="X86" t="s">
         <v>385</v>
       </c>
-      <c r="Y86" t="n">
+      <c r="Y86">
         <v>1</v>
       </c>
-      <c r="Z86" t="n">
+      <c r="Z86">
         <v>1</v>
       </c>
       <c r="AA86" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" t="n">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A87">
         <v>86</v>
       </c>
       <c r="B87" t="s">
@@ -7594,21 +7015,20 @@
       <c r="E87" t="s">
         <v>386</v>
       </c>
-      <c r="F87"/>
-      <c r="G87" t="n">
+      <c r="G87">
         <v>208984000000</v>
       </c>
       <c r="H87" t="s">
         <v>40</v>
       </c>
-      <c r="I87" t="n">
+      <c r="I87">
         <v>39669</v>
       </c>
       <c r="J87" t="s">
         <v>31</v>
       </c>
-      <c r="K87" t="n">
-        <v>1.815</v>
+      <c r="K87">
+        <v>1.8149999999999999</v>
       </c>
       <c r="L87" t="s">
         <v>51</v>
@@ -7619,36 +7039,30 @@
       <c r="N87" t="s">
         <v>34</v>
       </c>
-      <c r="O87"/>
-      <c r="P87"/>
-      <c r="Q87" t="n">
+      <c r="Q87">
         <v>25</v>
       </c>
-      <c r="R87"/>
-      <c r="S87"/>
       <c r="T87" t="b">
         <v>0</v>
       </c>
       <c r="U87" t="s">
         <v>388</v>
       </c>
-      <c r="V87"/>
-      <c r="W87"/>
       <c r="X87" t="s">
         <v>389</v>
       </c>
-      <c r="Y87" t="n">
+      <c r="Y87">
         <v>2</v>
       </c>
-      <c r="Z87" t="n">
+      <c r="Z87">
         <v>1</v>
       </c>
       <c r="AA87" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="n">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A88">
         <v>87</v>
       </c>
       <c r="B88" t="s">
@@ -7663,21 +7077,20 @@
       <c r="E88" t="s">
         <v>390</v>
       </c>
-      <c r="F88"/>
-      <c r="G88" t="n">
+      <c r="G88">
         <v>208984000000</v>
       </c>
       <c r="H88" t="s">
         <v>45</v>
       </c>
-      <c r="I88" t="n">
+      <c r="I88">
         <v>39702</v>
       </c>
       <c r="J88" t="s">
         <v>31</v>
       </c>
-      <c r="K88" t="n">
-        <v>1.815</v>
+      <c r="K88">
+        <v>1.8149999999999999</v>
       </c>
       <c r="L88" t="s">
         <v>51</v>
@@ -7688,36 +7101,30 @@
       <c r="N88" t="s">
         <v>34</v>
       </c>
-      <c r="O88"/>
-      <c r="P88"/>
-      <c r="Q88" t="n">
+      <c r="Q88">
         <v>34.4</v>
       </c>
-      <c r="R88"/>
-      <c r="S88"/>
       <c r="T88" t="b">
         <v>0</v>
       </c>
       <c r="U88" t="s">
         <v>392</v>
       </c>
-      <c r="V88"/>
-      <c r="W88"/>
       <c r="X88" t="s">
         <v>393</v>
       </c>
-      <c r="Y88" t="n">
+      <c r="Y88">
         <v>3</v>
       </c>
-      <c r="Z88" t="n">
+      <c r="Z88">
         <v>1</v>
       </c>
       <c r="AA88" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="n">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A89">
         <v>88</v>
       </c>
       <c r="B89" t="s">
@@ -7732,20 +7139,19 @@
       <c r="E89" t="s">
         <v>394</v>
       </c>
-      <c r="F89"/>
-      <c r="G89" t="n">
+      <c r="G89">
         <v>208984000000</v>
       </c>
       <c r="H89" t="s">
         <v>50</v>
       </c>
-      <c r="I89" t="n">
+      <c r="I89">
         <v>39758</v>
       </c>
       <c r="J89" t="s">
         <v>31</v>
       </c>
-      <c r="K89" t="n">
+      <c r="K89">
         <v>1.722</v>
       </c>
       <c r="L89" t="s">
@@ -7757,36 +7163,30 @@
       <c r="N89" t="s">
         <v>34</v>
       </c>
-      <c r="O89"/>
-      <c r="P89"/>
-      <c r="Q89" t="n">
+      <c r="Q89">
         <v>23.8</v>
       </c>
-      <c r="R89"/>
-      <c r="S89"/>
       <c r="T89" t="b">
         <v>0</v>
       </c>
       <c r="U89" t="s">
         <v>396</v>
       </c>
-      <c r="V89"/>
-      <c r="W89"/>
       <c r="X89" t="s">
         <v>397</v>
       </c>
-      <c r="Y89" t="n">
+      <c r="Y89">
         <v>4</v>
       </c>
-      <c r="Z89" t="n">
+      <c r="Z89">
         <v>1</v>
       </c>
       <c r="AA89" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A90">
         <v>89</v>
       </c>
       <c r="B90" t="s">
@@ -7801,20 +7201,19 @@
       <c r="E90" t="s">
         <v>398</v>
       </c>
-      <c r="F90"/>
-      <c r="G90" t="n">
+      <c r="G90">
         <v>208984000000</v>
       </c>
       <c r="H90" t="s">
         <v>56</v>
       </c>
-      <c r="I90" t="n">
+      <c r="I90">
         <v>39718</v>
       </c>
       <c r="J90" t="s">
         <v>31</v>
       </c>
-      <c r="K90" t="n">
+      <c r="K90">
         <v>1.744</v>
       </c>
       <c r="L90" t="s">
@@ -7826,36 +7225,30 @@
       <c r="N90" t="s">
         <v>34</v>
       </c>
-      <c r="O90"/>
-      <c r="P90"/>
-      <c r="Q90" t="n">
+      <c r="Q90">
         <v>25.5</v>
       </c>
-      <c r="R90"/>
-      <c r="S90"/>
       <c r="T90" t="b">
         <v>0</v>
       </c>
       <c r="U90" t="s">
         <v>400</v>
       </c>
-      <c r="V90"/>
-      <c r="W90"/>
       <c r="X90" t="s">
         <v>401</v>
       </c>
-      <c r="Y90" t="n">
+      <c r="Y90">
         <v>5</v>
       </c>
-      <c r="Z90" t="n">
+      <c r="Z90">
         <v>1</v>
       </c>
       <c r="AA90" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="n">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A91">
         <v>90</v>
       </c>
       <c r="B91" t="s">
@@ -7870,21 +7263,20 @@
       <c r="E91" t="s">
         <v>402</v>
       </c>
-      <c r="F91"/>
-      <c r="G91" t="n">
+      <c r="G91">
         <v>208984000000</v>
       </c>
       <c r="H91" t="s">
         <v>61</v>
       </c>
-      <c r="I91" t="n">
+      <c r="I91">
         <v>40097</v>
       </c>
       <c r="J91" t="s">
         <v>31</v>
       </c>
-      <c r="K91" t="n">
-        <v>0.356</v>
+      <c r="K91">
+        <v>0.35599999999999998</v>
       </c>
       <c r="L91" t="s">
         <v>32</v>
@@ -7895,36 +7287,30 @@
       <c r="N91" t="s">
         <v>34</v>
       </c>
-      <c r="O91"/>
-      <c r="P91"/>
-      <c r="Q91" t="n">
+      <c r="Q91">
         <v>14.9</v>
       </c>
-      <c r="R91"/>
-      <c r="S91"/>
       <c r="T91" t="b">
         <v>0</v>
       </c>
       <c r="U91" t="s">
         <v>404</v>
       </c>
-      <c r="V91"/>
-      <c r="W91"/>
       <c r="X91" t="s">
         <v>405</v>
       </c>
-      <c r="Y91" t="n">
+      <c r="Y91">
         <v>6</v>
       </c>
-      <c r="Z91" t="n">
+      <c r="Z91">
         <v>1</v>
       </c>
       <c r="AA91" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" t="n">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A92">
         <v>91</v>
       </c>
       <c r="B92" t="s">
@@ -7939,20 +7325,19 @@
       <c r="E92" t="s">
         <v>406</v>
       </c>
-      <c r="F92"/>
-      <c r="G92" t="n">
+      <c r="G92">
         <v>208984000000</v>
       </c>
       <c r="H92" t="s">
         <v>66</v>
       </c>
-      <c r="I92" t="n">
+      <c r="I92">
         <v>40147</v>
       </c>
       <c r="J92" t="s">
         <v>31</v>
       </c>
-      <c r="K92" t="n">
+      <c r="K92">
         <v>0.216</v>
       </c>
       <c r="L92" t="s">
@@ -7964,36 +7349,30 @@
       <c r="N92" t="s">
         <v>34</v>
       </c>
-      <c r="O92"/>
-      <c r="P92"/>
-      <c r="Q92" t="n">
+      <c r="Q92">
         <v>14.9</v>
       </c>
-      <c r="R92"/>
-      <c r="S92"/>
       <c r="T92" t="b">
         <v>0</v>
       </c>
       <c r="U92" t="s">
         <v>408</v>
       </c>
-      <c r="V92"/>
-      <c r="W92"/>
       <c r="X92" t="s">
         <v>409</v>
       </c>
-      <c r="Y92" t="n">
+      <c r="Y92">
         <v>1</v>
       </c>
-      <c r="Z92" t="n">
+      <c r="Z92">
         <v>2</v>
       </c>
       <c r="AA92" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" t="n">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A93">
         <v>92</v>
       </c>
       <c r="B93" t="s">
@@ -8008,20 +7387,19 @@
       <c r="E93" t="s">
         <v>410</v>
       </c>
-      <c r="F93"/>
-      <c r="G93" t="n">
+      <c r="G93">
         <v>208984000000</v>
       </c>
       <c r="H93" t="s">
         <v>71</v>
       </c>
-      <c r="I93" t="n">
+      <c r="I93">
         <v>40130</v>
       </c>
       <c r="J93" t="s">
         <v>31</v>
       </c>
-      <c r="K93" t="n">
+      <c r="K93">
         <v>0.252</v>
       </c>
       <c r="L93" t="s">
@@ -8033,36 +7411,30 @@
       <c r="N93" t="s">
         <v>34</v>
       </c>
-      <c r="O93"/>
-      <c r="P93"/>
-      <c r="Q93" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R93"/>
-      <c r="S93"/>
+      <c r="Q93">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T93" t="b">
         <v>0</v>
       </c>
       <c r="U93" t="s">
         <v>412</v>
       </c>
-      <c r="V93"/>
-      <c r="W93"/>
       <c r="X93" t="s">
         <v>413</v>
       </c>
-      <c r="Y93" t="n">
+      <c r="Y93">
         <v>2</v>
       </c>
-      <c r="Z93" t="n">
+      <c r="Z93">
         <v>2</v>
       </c>
       <c r="AA93" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="n">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A94">
         <v>93</v>
       </c>
       <c r="B94" t="s">
@@ -8077,21 +7449,20 @@
       <c r="E94" t="s">
         <v>414</v>
       </c>
-      <c r="F94"/>
-      <c r="G94" t="n">
+      <c r="G94">
         <v>208984000000</v>
       </c>
       <c r="H94" t="s">
         <v>76</v>
       </c>
-      <c r="I94" t="n">
+      <c r="I94">
         <v>40152</v>
       </c>
       <c r="J94" t="s">
         <v>31</v>
       </c>
-      <c r="K94" t="n">
-        <v>0.203</v>
+      <c r="K94">
+        <v>0.20300000000000001</v>
       </c>
       <c r="L94" t="s">
         <v>32</v>
@@ -8102,36 +7473,30 @@
       <c r="N94" t="s">
         <v>34</v>
       </c>
-      <c r="O94"/>
-      <c r="P94"/>
-      <c r="Q94" t="n">
-        <v>18.9</v>
-      </c>
-      <c r="R94"/>
-      <c r="S94"/>
+      <c r="Q94">
+        <v>18.899999999999999</v>
+      </c>
       <c r="T94" t="b">
         <v>0</v>
       </c>
       <c r="U94" t="s">
         <v>416</v>
       </c>
-      <c r="V94"/>
-      <c r="W94"/>
       <c r="X94" t="s">
         <v>417</v>
       </c>
-      <c r="Y94" t="n">
+      <c r="Y94">
         <v>3</v>
       </c>
-      <c r="Z94" t="n">
+      <c r="Z94">
         <v>2</v>
       </c>
       <c r="AA94" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="n">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A95">
         <v>94</v>
       </c>
       <c r="B95" t="s">
@@ -8146,20 +7511,19 @@
       <c r="E95" t="s">
         <v>418</v>
       </c>
-      <c r="F95"/>
-      <c r="G95" t="n">
+      <c r="G95">
         <v>208984000000</v>
       </c>
       <c r="H95" t="s">
         <v>81</v>
       </c>
-      <c r="I95" t="n">
+      <c r="I95">
         <v>40170</v>
       </c>
       <c r="J95" t="s">
         <v>31</v>
       </c>
-      <c r="K95" t="n">
+      <c r="K95">
         <v>0.126</v>
       </c>
       <c r="L95" t="s">
@@ -8171,36 +7535,30 @@
       <c r="N95" t="s">
         <v>34</v>
       </c>
-      <c r="O95"/>
-      <c r="P95"/>
-      <c r="Q95" t="n">
+      <c r="Q95">
         <v>11.3</v>
       </c>
-      <c r="R95"/>
-      <c r="S95"/>
       <c r="T95" t="b">
         <v>0</v>
       </c>
       <c r="U95" t="s">
         <v>420</v>
       </c>
-      <c r="V95"/>
-      <c r="W95"/>
       <c r="X95" t="s">
         <v>421</v>
       </c>
-      <c r="Y95" t="n">
+      <c r="Y95">
         <v>4</v>
       </c>
-      <c r="Z95" t="n">
+      <c r="Z95">
         <v>2</v>
       </c>
       <c r="AA95" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="n">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A96">
         <v>95</v>
       </c>
       <c r="B96" t="s">
@@ -8215,21 +7573,20 @@
       <c r="E96" t="s">
         <v>422</v>
       </c>
-      <c r="F96"/>
-      <c r="G96" t="n">
+      <c r="G96">
         <v>208984000000</v>
       </c>
       <c r="H96" t="s">
         <v>86</v>
       </c>
-      <c r="I96" t="n">
+      <c r="I96">
         <v>39894</v>
       </c>
       <c r="J96" t="s">
         <v>31</v>
       </c>
-      <c r="K96" t="n">
-        <v>1.481</v>
+      <c r="K96">
+        <v>1.4810000000000001</v>
       </c>
       <c r="L96" t="s">
         <v>32</v>
@@ -8240,36 +7597,30 @@
       <c r="N96" t="s">
         <v>34</v>
       </c>
-      <c r="O96"/>
-      <c r="P96"/>
-      <c r="Q96" t="n">
+      <c r="Q96">
         <v>18.7</v>
       </c>
-      <c r="R96"/>
-      <c r="S96"/>
       <c r="T96" t="b">
         <v>0</v>
       </c>
       <c r="U96" t="s">
         <v>424</v>
       </c>
-      <c r="V96"/>
-      <c r="W96"/>
       <c r="X96" t="s">
         <v>425</v>
       </c>
-      <c r="Y96" t="n">
+      <c r="Y96">
         <v>5</v>
       </c>
-      <c r="Z96" t="n">
+      <c r="Z96">
         <v>2</v>
       </c>
       <c r="AA96" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="n">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A97">
         <v>96</v>
       </c>
       <c r="B97" t="s">
@@ -8284,21 +7635,20 @@
       <c r="E97" t="s">
         <v>426</v>
       </c>
-      <c r="F97"/>
-      <c r="G97" t="n">
+      <c r="G97">
         <v>208984000000</v>
       </c>
       <c r="H97" t="s">
         <v>91</v>
       </c>
-      <c r="I97" t="n">
+      <c r="I97">
         <v>39437</v>
       </c>
       <c r="J97" t="s">
         <v>31</v>
       </c>
-      <c r="K97" t="n">
-        <v>2.261</v>
+      <c r="K97">
+        <v>2.2610000000000001</v>
       </c>
       <c r="L97" t="s">
         <v>51</v>
@@ -8309,28 +7659,22 @@
       <c r="N97" t="s">
         <v>34</v>
       </c>
-      <c r="O97"/>
-      <c r="P97"/>
-      <c r="Q97" t="n">
+      <c r="Q97">
         <v>14.9</v>
       </c>
-      <c r="R97"/>
-      <c r="S97"/>
       <c r="T97" t="b">
         <v>0</v>
       </c>
       <c r="U97" t="s">
         <v>428</v>
       </c>
-      <c r="V97"/>
-      <c r="W97"/>
       <c r="X97" t="s">
         <v>429</v>
       </c>
-      <c r="Y97" t="n">
+      <c r="Y97">
         <v>6</v>
       </c>
-      <c r="Z97" t="n">
+      <c r="Z97">
         <v>2</v>
       </c>
       <c r="AA97" t="s">
@@ -8339,6 +7683,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>